--- a/OPRA Model.xlsx
+++ b/OPRA Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745C1CF9-A9A2-4DF3-BC25-C4EDC9B34820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D8047F-B552-4891-9559-E697C17B06F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22944" yWindow="0" windowWidth="33432" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21852" yWindow="2832" windowWidth="23040" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="71">
   <si>
     <t>OPERA LIMITED ($OPRA)</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>REVENUE BY SEGMENT ($mm)</t>
+  </si>
+  <si>
+    <t>CAGR</t>
   </si>
 </sst>
 </file>
@@ -873,7 +876,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="7">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="8">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -902,9 +905,9 @@
     <col min="2" max="2" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="37" t="s">
         <v>0</v>
       </c>
@@ -917,8 +920,9 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="37"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -929,8 +933,9 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-    </row>
-    <row r="6" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="3"/>
+    </row>
+    <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -961,14 +966,17 @@
       <c r="K6" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="2:11" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -1004,8 +1012,12 @@
         <f>J9*1.05</f>
         <v>300.71084400000001</v>
       </c>
-    </row>
-    <row r="10" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="31">
+        <f>(K9/F9)^(1/5)-1</f>
+        <v>1.1500612074110794E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -1023,35 +1035,39 @@
       </c>
       <c r="F10" s="4">
         <f t="shared" si="0"/>
-        <v>2.1219307394366198</v>
+        <v>2.1391813732394365</v>
       </c>
       <c r="G10" s="4">
         <f>G25/G9</f>
-        <v>2.4888370311152634</v>
+        <v>2.480216684392067</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" ref="H10:K10" si="1">H25/H9</f>
-        <v>2.8793915078847721</v>
+        <v>2.8682203726806899</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="1"/>
-        <v>3.1356939432562942</v>
+        <v>3.1027603867472324</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="1"/>
-        <v>3.226633643702228</v>
+        <v>3.1915106504389725</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" si="1"/>
-        <v>3.2765162553082972</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.2399363621340047</v>
+      </c>
+      <c r="L10" s="31">
+        <f>(K10/F10)^(1/5)-1</f>
+        <v>8.6570160774116056E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>12</v>
       </c>
@@ -1065,31 +1081,35 @@
         <v>293.44799999999998</v>
       </c>
       <c r="F13" s="12">
-        <f>E13*1.33</f>
-        <v>390.28584000000001</v>
+        <f>E13*1.34</f>
+        <v>393.22032000000002</v>
       </c>
       <c r="G13" s="12">
-        <f>F13*1.2</f>
-        <v>468.343008</v>
+        <f>F13*1.18</f>
+        <v>463.99997759999997</v>
       </c>
       <c r="H13" s="12">
         <f>G13*1.17</f>
-        <v>547.96131935999995</v>
+        <v>542.87997379199987</v>
       </c>
       <c r="I13" s="12">
-        <f>H13*1.11</f>
-        <v>608.23706448960002</v>
+        <f>H13*1.1</f>
+        <v>597.16797117119995</v>
       </c>
       <c r="J13" s="12">
         <f>I13*1.1</f>
-        <v>669.06077093856004</v>
+        <v>656.88476828831995</v>
       </c>
       <c r="K13" s="12">
         <f>J13*1.08</f>
-        <v>722.58563261364486</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>709.43554975138557</v>
+      </c>
+      <c r="L13" s="31">
+        <f t="shared" ref="L13:L17" si="2">(K13/F13)^(1/5)-1</f>
+        <v>0.12526652375986003</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -1097,76 +1117,78 @@
         <v>0.626</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" ref="D14:K14" si="2">D13/D25</f>
+        <f t="shared" ref="D14:K14" si="3">D13/D25</f>
         <v>0.58206724844831625</v>
       </c>
       <c r="E14" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.61052579018325259</v>
       </c>
       <c r="F14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.64763938329948745</v>
+        <f t="shared" si="3"/>
+        <v>0.64724693701524727</v>
       </c>
       <c r="G14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.67611903855736633</v>
+        <f t="shared" si="3"/>
+        <v>0.67217741963452315</v>
       </c>
       <c r="H14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.69771601520205406</v>
+        <f t="shared" si="3"/>
+        <v>0.69393822944247896</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.71116229518622076</v>
+        <f t="shared" si="3"/>
+        <v>0.70563120282421421</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.72402926119498734</v>
+        <f t="shared" si="3"/>
+        <v>0.71867593570076693</v>
       </c>
       <c r="K14" s="13">
-        <f t="shared" si="2"/>
-        <v>0.73337804704549059</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0.72816093791359393</v>
+      </c>
+      <c r="L14" s="31"/>
+    </row>
+    <row r="15" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" ref="D15:K15" si="3">D13/C13-1</f>
+        <f t="shared" ref="D15:K15" si="4">D13/C13-1</f>
         <v>0.86409490759422147</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.27044765780587054</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
-        <v>0.33000000000000007</v>
+        <f t="shared" si="4"/>
+        <v>0.34000000000000008</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="4"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
-        <v>0.16999999999999993</v>
+        <f t="shared" si="4"/>
+        <v>0.16999999999999971</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="4"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="J15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="K15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000071E-2</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="31"/>
+    </row>
+    <row r="17" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
@@ -1180,31 +1202,35 @@
         <v>186.273</v>
       </c>
       <c r="F17" s="12">
-        <f>E17*1.13</f>
-        <v>210.48848999999998</v>
+        <f>E17*1.14</f>
+        <v>212.35121999999998</v>
       </c>
       <c r="G17" s="12">
         <f>F17*1.05</f>
-        <v>221.01291449999999</v>
+        <v>222.96878099999998</v>
       </c>
       <c r="H17" s="12">
         <f>G17*1.05</f>
-        <v>232.063560225</v>
+        <v>234.11722004999999</v>
       </c>
       <c r="I17" s="12">
         <f>H17*1.03</f>
-        <v>239.02546703175</v>
+        <v>241.14073665149999</v>
       </c>
       <c r="J17" s="12">
         <f>I17*1.02</f>
-        <v>243.805976372385</v>
+        <v>245.96355138453001</v>
       </c>
       <c r="K17" s="12">
         <f>J17*1.02</f>
-        <v>248.68209589983272</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>250.88282241222061</v>
+      </c>
+      <c r="L17" s="31">
+        <f t="shared" si="2"/>
+        <v>3.391118419521022E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>13</v>
       </c>
@@ -1212,76 +1238,76 @@
         <v>0.373</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" ref="D18:K18" si="4">D17/D25</f>
+        <f t="shared" ref="D18:K18" si="5">D17/D25</f>
         <v>0.40866170900669563</v>
       </c>
       <c r="E18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.38754556348928948</v>
       </c>
       <c r="F18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.34928409356393847</v>
+        <f t="shared" si="5"/>
+        <v>0.34953350507535036</v>
       </c>
       <c r="G18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.31906324362271976</v>
+        <f t="shared" si="5"/>
+        <v>0.32300557566155169</v>
       </c>
       <c r="H18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.29548520450841209</v>
+        <f t="shared" si="5"/>
+        <v>0.29926115717382967</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.27947310295024641</v>
+        <f t="shared" si="5"/>
+        <v>0.28493897239598187</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.2638365132365989</v>
+        <f t="shared" si="5"/>
+        <v>0.26910060024709492</v>
       </c>
       <c r="K18" s="13">
-        <f t="shared" si="4"/>
-        <v>0.25239636881032945</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>0.25750481680557397</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" ref="D19:K19" si="5">D17/C17-1</f>
+        <f t="shared" ref="D19:K19" si="6">D17/C17-1</f>
         <v>0.32968186290587087</v>
       </c>
       <c r="E19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.14864214888264016</v>
       </c>
       <c r="F19" s="13">
-        <f t="shared" si="5"/>
-        <v>0.12999999999999989</v>
+        <f t="shared" si="6"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="G19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="H19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="K19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
@@ -1291,7 +1317,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
     </row>
-    <row r="21" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
         <v>53</v>
       </c>
@@ -1305,31 +1331,35 @@
         <v>0.92700000000000005</v>
       </c>
       <c r="F21" s="12">
-        <f>E21*2</f>
-        <v>1.8540000000000001</v>
+        <f>E21*2.11</f>
+        <v>1.95597</v>
       </c>
       <c r="G21" s="12">
-        <f>F21*1.8</f>
-        <v>3.3372000000000002</v>
+        <f>F21*1.7</f>
+        <v>3.3251489999999997</v>
       </c>
       <c r="H21" s="12">
         <f>G21*1.6</f>
-        <v>5.3395200000000003</v>
+        <v>5.3202384</v>
       </c>
       <c r="I21" s="12">
         <f>H21*1.5</f>
-        <v>8.0092800000000004</v>
+        <v>7.9803575999999996</v>
       </c>
       <c r="J21" s="12">
         <f>I21*1.4</f>
-        <v>11.212992</v>
+        <v>11.172500639999999</v>
       </c>
       <c r="K21" s="12">
         <f>J21*1.25</f>
-        <v>14.01624</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13.965625799999998</v>
+      </c>
+      <c r="L21" s="31">
+        <f t="shared" ref="L21" si="7">(K21/F21)^(1/5)-1</f>
+        <v>0.48162958838159176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>13</v>
       </c>
@@ -1345,31 +1375,31 @@
         <v>1.9286463274579321E-3</v>
       </c>
       <c r="F22" s="13">
-        <f t="shared" ref="F22" si="6">F21/F30</f>
-        <v>3.0765231365740804E-3</v>
+        <f t="shared" ref="F22" si="8">F21/F30</f>
+        <v>3.2195579094023248E-3</v>
       </c>
       <c r="G22" s="13">
-        <f t="shared" ref="G22" si="7">G21/G30</f>
-        <v>4.8177178199138243E-3</v>
+        <f t="shared" ref="G22" si="9">G21/G30</f>
+        <v>4.8170047039250439E-3</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" ref="H22" si="8">H21/H30</f>
-        <v>6.7987802895337424E-3</v>
+        <f t="shared" ref="H22" si="10">H21/H30</f>
+        <v>6.8006133836913561E-3</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" ref="I22" si="9">I21/I30</f>
-        <v>9.3646018635329085E-3</v>
+        <f t="shared" ref="I22" si="11">I21/I30</f>
+        <v>9.429824779803829E-3</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" ref="J22" si="10">J21/J30</f>
-        <v>1.2134225568413769E-2</v>
+        <f t="shared" ref="J22" si="12">J21/J30</f>
+        <v>1.222346405213821E-2</v>
       </c>
       <c r="K22" s="13">
-        <f t="shared" ref="K22" si="11">K21/K30</f>
-        <v>1.4225584144179926E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="K22" si="13">K21/K30</f>
+        <v>1.4334245280832042E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>14</v>
       </c>
@@ -1382,31 +1412,31 @@
         <v>-0.7480293558032074</v>
       </c>
       <c r="F23" s="30">
-        <f t="shared" ref="F23:K23" si="12">F21/E21-1</f>
-        <v>1</v>
+        <f t="shared" ref="F23:K23" si="14">F21/E21-1</f>
+        <v>1.1099999999999999</v>
       </c>
       <c r="G23" s="30">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="14"/>
+        <v>0.7</v>
       </c>
       <c r="H23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="I23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.5</v>
       </c>
       <c r="J23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="K23" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="23"/>
@@ -1416,7 +1446,7 @@
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
     </row>
-    <row r="25" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="24" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1455,7 @@
         <v>251.08</v>
       </c>
       <c r="D25" s="25">
-        <f t="shared" ref="D25" si="13">D21+D17+D13</f>
+        <f t="shared" ref="D25" si="15">D21+D17+D13</f>
         <v>396.827</v>
       </c>
       <c r="E25" s="25">
@@ -1434,30 +1464,34 @@
       </c>
       <c r="F25" s="25">
         <f>F13+F17+F21</f>
-        <v>602.62833000000001</v>
+        <v>607.52751000000001</v>
       </c>
       <c r="G25" s="25">
         <f>G13+G17+G21</f>
-        <v>692.69312250000007</v>
+        <v>690.29390760000001</v>
       </c>
       <c r="H25" s="25">
-        <f t="shared" ref="H25:K25" si="14">H13+H17+H21</f>
-        <v>785.364399585</v>
+        <f t="shared" ref="H25:K25" si="16">H13+H17+H21</f>
+        <v>782.31743224199988</v>
       </c>
       <c r="I25" s="25">
-        <f t="shared" si="14"/>
-        <v>855.27181152134995</v>
+        <f t="shared" si="16"/>
+        <v>846.28906542269999</v>
       </c>
       <c r="J25" s="25">
-        <f t="shared" si="14"/>
-        <v>924.079739310945</v>
+        <f t="shared" si="16"/>
+        <v>914.02082031284988</v>
       </c>
       <c r="K25" s="25">
-        <f t="shared" si="14"/>
-        <v>985.28396851347759</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="16"/>
+        <v>974.28399796360623</v>
+      </c>
+      <c r="L25" s="31">
+        <f t="shared" ref="L25" si="17">(K25/F25)^(1/5)-1</f>
+        <v>9.9066382684483312E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>14</v>
       </c>
@@ -1465,39 +1499,39 @@
         <v>0.252</v>
       </c>
       <c r="D26" s="13">
-        <f t="shared" ref="D26:K26" si="15">D25/C25-1</f>
+        <f t="shared" ref="D26:K26" si="18">D25/C25-1</f>
         <v>0.58048032499601709</v>
       </c>
       <c r="E26" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.2112280666386106</v>
       </c>
       <c r="F26" s="13">
-        <f t="shared" si="15"/>
-        <v>0.25378308034153907</v>
+        <f t="shared" si="18"/>
+        <v>0.26397594497428489</v>
       </c>
       <c r="G26" s="13">
-        <f t="shared" si="15"/>
-        <v>0.14945329984735389</v>
+        <f t="shared" si="18"/>
+        <v>0.1362348144530936</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="15"/>
-        <v>0.13378402942783651</v>
+        <f t="shared" si="18"/>
+        <v>0.13331064294330131</v>
       </c>
       <c r="I26" s="13">
-        <f t="shared" si="15"/>
-        <v>8.901270795224514E-2</v>
+        <f t="shared" si="18"/>
+        <v>8.1771964351308624E-2</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="15"/>
-        <v>8.0451532323040142E-2</v>
+        <f t="shared" si="18"/>
+        <v>8.0033829642262466E-2</v>
       </c>
       <c r="K26" s="13">
-        <f t="shared" si="15"/>
-        <v>6.6232627552434531E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>6.593195287403808E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>54</v>
       </c>
@@ -1528,50 +1562,57 @@
       <c r="K28" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="2:11" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="14">
-        <f t="shared" ref="C30:K30" si="16">C25</f>
+        <f t="shared" ref="C30:K30" si="19">C25</f>
         <v>251.08</v>
       </c>
       <c r="D30" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>396.827</v>
       </c>
       <c r="E30" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>480.64799999999997</v>
       </c>
       <c r="F30" s="14">
-        <f t="shared" si="16"/>
-        <v>602.62833000000001</v>
+        <f t="shared" si="19"/>
+        <v>607.52751000000001</v>
       </c>
       <c r="G30" s="14">
-        <f t="shared" si="16"/>
-        <v>692.69312250000007</v>
+        <f t="shared" si="19"/>
+        <v>690.29390760000001</v>
       </c>
       <c r="H30" s="14">
-        <f t="shared" si="16"/>
-        <v>785.364399585</v>
+        <f t="shared" si="19"/>
+        <v>782.31743224199988</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="16"/>
-        <v>855.27181152134995</v>
+        <f t="shared" si="19"/>
+        <v>846.28906542269999</v>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="16"/>
-        <v>924.079739310945</v>
+        <f t="shared" si="19"/>
+        <v>914.02082031284988</v>
       </c>
       <c r="K30" s="14">
-        <f t="shared" si="16"/>
-        <v>985.28396851347759</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="19"/>
+        <v>974.28399796360623</v>
+      </c>
+      <c r="L30" s="31">
+        <f t="shared" ref="L30:L32" si="20">(K30/F30)^(1/5)-1</f>
+        <v>9.9066382684483312E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>18</v>
       </c>
@@ -1589,149 +1630,154 @@
       </c>
       <c r="G32" s="12">
         <f>G30*0.345</f>
-        <v>238.97912726250001</v>
+        <v>238.15139812199999</v>
       </c>
       <c r="H32" s="12">
         <f>H30*0.34</f>
-        <v>267.0238958589</v>
+        <v>265.98792696227997</v>
       </c>
       <c r="I32" s="12">
         <f>I30*0.335</f>
-        <v>286.51605685965222</v>
+        <v>283.50683691660453</v>
       </c>
       <c r="J32" s="12">
         <f>J30*0.33</f>
-        <v>304.94631397261185</v>
+        <v>301.62687070324046</v>
       </c>
       <c r="K32" s="12">
         <f>K30*0.328</f>
-        <v>323.17314167242068</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>319.56515133206284</v>
+      </c>
+      <c r="L32" s="31"/>
+    </row>
+    <row r="33" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="13">
-        <f t="shared" ref="C33:K33" si="17">C32/C30</f>
+        <f t="shared" ref="C33:K33" si="21">C32/C30</f>
         <v>0.21746057033614782</v>
       </c>
       <c r="D33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.23486305115327336</v>
       </c>
       <c r="E33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.27587756528686275</v>
       </c>
       <c r="F33" s="13">
-        <f t="shared" si="17"/>
-        <v>0.34963507274873717</v>
+        <f t="shared" si="21"/>
+        <v>0.34681557054099488</v>
       </c>
       <c r="G33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.34499999999999997</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.34</v>
       </c>
       <c r="I33" s="13">
-        <f t="shared" si="17"/>
-        <v>0.33499999999999996</v>
+        <f t="shared" si="21"/>
+        <v>0.33500000000000002</v>
       </c>
       <c r="J33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.33</v>
       </c>
       <c r="K33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="14">
-        <f t="shared" ref="C35:K35" si="18">C30-C32</f>
+        <f t="shared" ref="C35:K35" si="22">C30-C32</f>
         <v>196.48000000000002</v>
       </c>
       <c r="D35" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>303.62700000000001</v>
       </c>
       <c r="E35" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>348.048</v>
       </c>
       <c r="F35" s="14">
-        <f t="shared" si="18"/>
-        <v>391.92833000000002</v>
+        <f t="shared" si="22"/>
+        <v>396.82751000000002</v>
       </c>
       <c r="G35" s="14">
-        <f t="shared" si="18"/>
-        <v>453.71399523750006</v>
+        <f t="shared" si="22"/>
+        <v>452.14250947800002</v>
       </c>
       <c r="H35" s="14">
-        <f t="shared" si="18"/>
-        <v>518.3405037261</v>
+        <f t="shared" si="22"/>
+        <v>516.32950527971991</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="18"/>
-        <v>568.75575466169767</v>
+        <f t="shared" si="22"/>
+        <v>562.78222850609541</v>
       </c>
       <c r="J35" s="14">
-        <f t="shared" si="18"/>
-        <v>619.13342533833315</v>
+        <f t="shared" si="22"/>
+        <v>612.39394960960942</v>
       </c>
       <c r="K35" s="14">
-        <f t="shared" si="18"/>
-        <v>662.11082684105691</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="22"/>
+        <v>654.71884663154333</v>
+      </c>
+      <c r="L35" s="31">
+        <f t="shared" ref="L35" si="23">(K35/F35)^(1/5)-1</f>
+        <v>0.10532658110063275</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="13">
-        <f t="shared" ref="C36:K36" si="19">C35/C30</f>
+        <f t="shared" ref="C36:K36" si="24">C35/C30</f>
         <v>0.78253942966385215</v>
       </c>
       <c r="D36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.76513694884672667</v>
       </c>
       <c r="E36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.72412243471313731</v>
       </c>
       <c r="F36" s="13">
-        <f t="shared" si="19"/>
-        <v>0.65036492725126283</v>
+        <f t="shared" si="24"/>
+        <v>0.65318442945900512</v>
       </c>
       <c r="G36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.65500000000000003</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.66</v>
       </c>
       <c r="I36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.66499999999999992</v>
       </c>
       <c r="J36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.67</v>
       </c>
       <c r="K36" s="13">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0.67199999999999993</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>22</v>
       </c>
@@ -1749,67 +1795,68 @@
       </c>
       <c r="G38" s="12">
         <f>G30*0.41</f>
-        <v>284.00418022500003</v>
+        <v>283.02050211599999</v>
       </c>
       <c r="H38" s="12">
         <f>H30*0.4</f>
-        <v>314.14575983400005</v>
+        <v>312.92697289679995</v>
       </c>
       <c r="I38" s="12">
         <f>I30*0.39</f>
-        <v>333.55600649332649</v>
+        <v>330.052735514853</v>
       </c>
       <c r="J38" s="12">
         <f>J30*0.38</f>
-        <v>351.15030093815909</v>
+        <v>347.32791171888294</v>
       </c>
       <c r="K38" s="12">
         <f>K30*0.37</f>
-        <v>364.5550683499867</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>360.48507924653433</v>
+      </c>
+      <c r="L38" s="31"/>
+    </row>
+    <row r="39" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" s="13">
-        <f t="shared" ref="C39:K39" si="20">C38/C30</f>
+        <f t="shared" ref="C39:K39" si="25">C38/C30</f>
         <v>0.80412617492432692</v>
       </c>
       <c r="D39" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.52692987120332035</v>
       </c>
       <c r="E39" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.48538639503337166</v>
       </c>
       <c r="F39" s="13">
-        <f t="shared" si="20"/>
-        <v>0.42480578369091943</v>
+        <f t="shared" si="25"/>
+        <v>0.42138009519931041</v>
       </c>
       <c r="G39" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.41</v>
       </c>
       <c r="H39" s="13">
-        <f t="shared" si="20"/>
-        <v>0.40000000000000008</v>
+        <f t="shared" si="25"/>
+        <v>0.4</v>
       </c>
       <c r="I39" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.39</v>
       </c>
       <c r="J39" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>0.38</v>
       </c>
       <c r="K39" s="13">
-        <f t="shared" si="20"/>
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="25"/>
+        <v>0.37000000000000005</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
         <v>23</v>
       </c>
@@ -1827,67 +1874,71 @@
       </c>
       <c r="G41" s="26">
         <f>G35-G38</f>
-        <v>169.70981501250003</v>
+        <v>169.12200736200003</v>
       </c>
       <c r="H41" s="26">
         <f>H35-H38</f>
-        <v>204.19474389209995</v>
+        <v>203.40253238291996</v>
       </c>
       <c r="I41" s="26">
         <f>I35-I38</f>
-        <v>235.19974816837117</v>
+        <v>232.72949299124241</v>
       </c>
       <c r="J41" s="26">
         <f>J35-J38</f>
-        <v>267.98312440017406</v>
+        <v>265.06603789072648</v>
       </c>
       <c r="K41" s="26">
         <f>K35-K38</f>
-        <v>297.55575849107021</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>294.233767385009</v>
+      </c>
+      <c r="L41" s="31">
+        <f t="shared" ref="L41" si="26">(K41/F41)^(1/5)-1</f>
+        <v>0.16792450199605158</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="13">
-        <f t="shared" ref="C42:K42" si="21">C41/C30</f>
+        <f t="shared" ref="C42:K42" si="27">C41/C30</f>
         <v>0.27122829377090962</v>
       </c>
       <c r="D42" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.23612304606289392</v>
       </c>
       <c r="E42" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.23988448927281505</v>
       </c>
       <c r="F42" s="13">
-        <f t="shared" si="21"/>
-        <v>0.22468243403027535</v>
+        <f t="shared" si="27"/>
+        <v>0.22287056597651028</v>
       </c>
       <c r="G42" s="13">
-        <f t="shared" si="21"/>
-        <v>0.24500000000000002</v>
+        <f t="shared" si="27"/>
+        <v>0.24500000000000005</v>
       </c>
       <c r="H42" s="13">
-        <f t="shared" si="21"/>
-        <v>0.25999999999999995</v>
+        <f t="shared" si="27"/>
+        <v>0.26</v>
       </c>
       <c r="I42" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.27499999999999991</v>
       </c>
       <c r="J42" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.29000000000000004</v>
       </c>
       <c r="K42" s="13">
-        <f t="shared" si="21"/>
-        <v>0.30199999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="27"/>
+        <v>0.30199999999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>25</v>
       </c>
@@ -1895,39 +1946,40 @@
         <v>17.600000000000001</v>
       </c>
       <c r="D44" s="12">
-        <f t="shared" ref="D44:K44" si="22">D30*0.032</f>
+        <f t="shared" ref="D44:K44" si="28">D30*0.032</f>
         <v>12.698464</v>
       </c>
       <c r="E44" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>15.380735999999999</v>
       </c>
       <c r="F44" s="12">
-        <f t="shared" si="22"/>
-        <v>19.284106560000001</v>
+        <f t="shared" si="28"/>
+        <v>19.440880320000002</v>
       </c>
       <c r="G44" s="12">
-        <f t="shared" si="22"/>
-        <v>22.166179920000001</v>
+        <f t="shared" si="28"/>
+        <v>22.089405043199999</v>
       </c>
       <c r="H44" s="12">
-        <f t="shared" si="22"/>
-        <v>25.131660786720001</v>
+        <f t="shared" si="28"/>
+        <v>25.034157831743997</v>
       </c>
       <c r="I44" s="12">
-        <f t="shared" si="22"/>
-        <v>27.3686979686832</v>
+        <f t="shared" si="28"/>
+        <v>27.0812500935264</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="22"/>
-        <v>29.57055165795024</v>
+        <f t="shared" si="28"/>
+        <v>29.248666250011198</v>
       </c>
       <c r="K44" s="12">
-        <f t="shared" si="22"/>
-        <v>31.529086992431285</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="28"/>
+        <v>31.177087934835399</v>
+      </c>
+      <c r="L44" s="31"/>
+    </row>
+    <row r="45" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>26</v>
       </c>
@@ -1942,30 +1994,31 @@
       </c>
       <c r="F45" s="12">
         <f>(F41-F44)*0.11</f>
-        <v>12.772748278400002</v>
+        <v>12.7555031648</v>
       </c>
       <c r="G45" s="12">
         <f>(G41-G44)*0.135</f>
-        <v>19.918390737487506</v>
+        <v>19.849401313038005</v>
       </c>
       <c r="H45" s="12">
         <f>(H41-H44)*0.145</f>
-        <v>25.96414705028009</v>
+        <v>25.863414309920515</v>
       </c>
       <c r="I45" s="12">
         <f>(I41-I44)*0.15</f>
-        <v>31.174657529953194</v>
+        <v>30.8472364346574</v>
       </c>
       <c r="J45" s="12">
         <f>(J41-J44)*0.16</f>
-        <v>38.146011638755816</v>
+        <v>37.730779462514448</v>
       </c>
       <c r="K45" s="12">
         <f>(K41-K44)*0.17</f>
-        <v>45.224534154768619</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>44.719635506529514</v>
+      </c>
+      <c r="L45" s="31"/>
+    </row>
+    <row r="46" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
@@ -1976,48 +2029,49 @@
       <c r="J46" s="12"/>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="21">
-        <f t="shared" ref="C47:K47" si="23">C41-C44-C45</f>
+        <f t="shared" ref="C47:K47" si="29">C41-C44-C45</f>
         <v>41.499999999999993</v>
       </c>
       <c r="D47" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>74.301535999999999</v>
       </c>
       <c r="E47" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>82.319264000000004</v>
       </c>
       <c r="F47" s="21">
-        <f t="shared" si="23"/>
-        <v>103.34314516160001</v>
+        <f t="shared" si="29"/>
+        <v>103.2036165152</v>
       </c>
       <c r="G47" s="21">
-        <f t="shared" si="23"/>
-        <v>127.62524435501254</v>
+        <f t="shared" si="29"/>
+        <v>127.18320100576203</v>
       </c>
       <c r="H47" s="21">
-        <f t="shared" si="23"/>
-        <v>153.09893605509984</v>
+        <f t="shared" si="29"/>
+        <v>152.50496024125545</v>
       </c>
       <c r="I47" s="21">
-        <f t="shared" si="23"/>
-        <v>176.65639266973477</v>
+        <f t="shared" si="29"/>
+        <v>174.80100646305863</v>
       </c>
       <c r="J47" s="21">
-        <f t="shared" si="23"/>
-        <v>200.26656110346801</v>
+        <f t="shared" si="29"/>
+        <v>198.08659217820085</v>
       </c>
       <c r="K47" s="22">
-        <f t="shared" si="23"/>
-        <v>220.8021373438703</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="29"/>
+        <v>218.33704394364406</v>
+      </c>
+      <c r="L47" s="31"/>
+    </row>
+    <row r="48" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D48" s="36"/>
       <c r="E48" s="36"/>
       <c r="F48" s="15"/>
@@ -2040,11 +2094,11 @@
         <v>17.16</v>
       </c>
       <c r="G49" s="12">
-        <f t="shared" ref="G49:H49" si="24">F49*1.1</f>
+        <f t="shared" ref="G49:H49" si="30">F49*1.1</f>
         <v>18.876000000000001</v>
       </c>
       <c r="H49" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>20.763600000000004</v>
       </c>
       <c r="I49" s="12">
@@ -2059,6 +2113,7 @@
         <f>J49*1.07</f>
         <v>25.913969452800011</v>
       </c>
+      <c r="L49" s="31"/>
     </row>
     <row r="50" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
@@ -2096,6 +2151,7 @@
         <f>J50*1.04</f>
         <v>17.656717478400001</v>
       </c>
+      <c r="L50" s="31"/>
     </row>
     <row r="51" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
@@ -2105,77 +2161,82 @@
         <v>6.1</v>
       </c>
       <c r="D51" s="12">
-        <f t="shared" ref="D51:K51" si="25">(D30-C30)*0.05</f>
+        <f t="shared" ref="D51:K51" si="31">(D30-C30)*0.05</f>
         <v>7.28735</v>
       </c>
       <c r="E51" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>4.1910499999999988</v>
       </c>
       <c r="F51" s="12">
-        <f t="shared" si="25"/>
-        <v>6.0990165000000021</v>
+        <f t="shared" si="31"/>
+        <v>6.3439755000000027</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="25"/>
-        <v>4.5032396250000035</v>
+        <f t="shared" si="31"/>
+        <v>4.1383198800000001</v>
       </c>
       <c r="H51" s="12">
-        <f t="shared" si="25"/>
-        <v>4.6335638542499966</v>
+        <f t="shared" si="31"/>
+        <v>4.601176232099994</v>
       </c>
       <c r="I51" s="12">
-        <f t="shared" si="25"/>
-        <v>3.4953705968174975</v>
+        <f t="shared" si="31"/>
+        <v>3.1985816590350056</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="25"/>
-        <v>3.4403963894797531</v>
+        <f t="shared" si="31"/>
+        <v>3.3865877445074943</v>
       </c>
       <c r="K51" s="12">
-        <f t="shared" si="25"/>
-        <v>3.0602114601266295</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>3.0131588825378177</v>
+      </c>
+      <c r="L51" s="31"/>
     </row>
     <row r="53" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="26">
-        <f t="shared" ref="C53:K53" si="26">C47+C49-C50-C51</f>
+        <f t="shared" ref="C53:K53" si="32">C47+C49-C50-C51</f>
         <v>41.099999999999987</v>
       </c>
       <c r="D53" s="26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>73.814185999999992</v>
       </c>
       <c r="E53" s="26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>70.428213999999997</v>
       </c>
       <c r="F53" s="26">
-        <f t="shared" si="26"/>
-        <v>101.2041286616</v>
+        <f t="shared" si="32"/>
+        <v>100.81964101519999</v>
       </c>
       <c r="G53" s="26">
-        <f t="shared" si="26"/>
-        <v>127.74200473001254</v>
+        <f t="shared" si="32"/>
+        <v>127.66488112576202</v>
       </c>
       <c r="H53" s="26">
-        <f t="shared" si="26"/>
-        <v>153.97505220084986</v>
+        <f t="shared" si="32"/>
+        <v>153.41346400915546</v>
       </c>
       <c r="I53" s="26">
-        <f t="shared" si="26"/>
-        <v>179.41655487291726</v>
+        <f t="shared" si="32"/>
+        <v>177.85795760402362</v>
       </c>
       <c r="J53" s="26">
-        <f t="shared" si="26"/>
-        <v>204.06721479398828</v>
+        <f t="shared" si="32"/>
+        <v>201.94105451369336</v>
       </c>
       <c r="K53" s="26">
-        <f t="shared" si="26"/>
-        <v>225.9991778581437</v>
+        <f t="shared" si="32"/>
+        <v>223.58113703550626</v>
+      </c>
+      <c r="L53" s="31">
+        <f t="shared" ref="L44:L53" si="33">(K53/F53)^(1/5)-1</f>
+        <v>0.17267590759370521</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2208,24 +2269,24 @@
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
       <c r="G56" s="15">
-        <f t="shared" ref="G56:K56" si="27">1/(1+$C$65)^G55</f>
-        <v>0.95681733101224009</v>
+        <f t="shared" ref="G56:K56" si="34">1/(1+$C$65)^G55</f>
+        <v>0.95680857147555853</v>
       </c>
       <c r="H56" s="15">
-        <f t="shared" si="27"/>
-        <v>0.87596569716400274</v>
+        <f t="shared" si="34"/>
+        <v>0.87594163933239222</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="27"/>
-        <v>0.80194607448869604</v>
+        <f t="shared" si="34"/>
+        <v>0.80190936660721424</v>
       </c>
       <c r="J56" s="15">
-        <f t="shared" si="27"/>
-        <v>0.73418115397665107</v>
+        <f t="shared" si="34"/>
+        <v>0.73413410594625594</v>
       </c>
       <c r="K56" s="15">
-        <f t="shared" si="27"/>
-        <v>0.67214240957305782</v>
+        <f t="shared" si="34"/>
+        <v>0.67208703122368529</v>
       </c>
       <c r="L56" s="15"/>
     </row>
@@ -2239,24 +2300,25 @@
       <c r="F57" s="26"/>
       <c r="G57" s="26">
         <f>G53*G56</f>
-        <v>122.22576402392355</v>
+        <v>122.15085253753736</v>
       </c>
       <c r="H57" s="26">
-        <f t="shared" ref="H57:K57" si="28">H53*H56</f>
-        <v>134.87686394698116</v>
+        <f t="shared" ref="H57:K57" si="35">H53*H56</f>
+        <v>134.38124115984058</v>
       </c>
       <c r="I57" s="26">
-        <f t="shared" si="28"/>
-        <v>143.88240187862172</v>
+        <f t="shared" si="35"/>
+        <v>142.62596212829536</v>
       </c>
       <c r="J57" s="26">
-        <f t="shared" si="28"/>
-        <v>149.82230324625144</v>
+        <f t="shared" si="35"/>
+        <v>148.25181550925441</v>
       </c>
       <c r="K57" s="26">
-        <f t="shared" si="28"/>
-        <v>151.90363196710277</v>
-      </c>
+        <f t="shared" si="35"/>
+        <v>150.26598262780936</v>
+      </c>
+      <c r="L57" s="31"/>
     </row>
     <row r="60" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
@@ -2289,31 +2351,33 @@
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="65" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C65" s="16">
-        <v>9.2299999999999993E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f>C62+(C63*C64)</f>
+        <v>9.2319999999999999E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C67" s="3"/>
     </row>
-    <row r="68" spans="2:3" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:6" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>39</v>
       </c>
       <c r="C69" s="12">
         <f>K57</f>
-        <v>151.90363196710277</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150.26598262780936</v>
+      </c>
+      <c r="F69" s="31"/>
+    </row>
+    <row r="70" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>40</v>
       </c>
@@ -2321,50 +2385,50 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C71" s="12">
         <f>C69*(1+C70)/(C65-C70)</f>
-        <v>2313.5397142092174</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2287.9178876040496</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C72" s="14">
         <f>C71*K56</f>
-        <v>1555.0281581515469</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1537.679940763371</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="2:3" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:6" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="12">
         <f>SUM(G57:K57)</f>
-        <v>702.71096506288063</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>697.67585396273694</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>42</v>
       </c>
       <c r="C77" s="12">
         <f>C72</f>
-        <v>1555.0281581515469</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1537.679940763371</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>45</v>
       </c>
@@ -2372,7 +2436,7 @@
         <v>-119</v>
       </c>
     </row>
-    <row r="79" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>56</v>
       </c>
@@ -2380,13 +2444,13 @@
         <v>258.3</v>
       </c>
     </row>
-    <row r="80" spans="2:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="28" t="s">
         <v>44</v>
       </c>
       <c r="C80" s="29">
         <f>C76+C77-C78+C79</f>
-        <v>2635.0391232144275</v>
+        <v>2612.6557947261081</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2420,7 +2484,7 @@
       </c>
       <c r="C85" s="27">
         <f>C80/C84</f>
-        <v>29.441777913010363</v>
+        <v>29.19168485727495</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2440,7 +2504,7 @@
       </c>
       <c r="C88" s="19">
         <f>C85/C87-1</f>
-        <v>1.3553422330408291</v>
+        <v>1.3353347885819962</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">

--- a/OPRA Model.xlsx
+++ b/OPRA Model.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D8047F-B552-4891-9559-E697C17B06F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB0487-47A8-4E8E-8C32-474901C83BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21852" yWindow="2832" windowWidth="23040" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="360" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
     <sheet name="Geographic Revenue" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -902,7 +902,8 @@
   <sheetFormatPr defaultColWidth="15.21875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="46.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" customWidth="1"/>
+    <col min="3" max="12" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1035,31 +1036,31 @@
       </c>
       <c r="F10" s="4">
         <f t="shared" si="0"/>
-        <v>2.1391813732394365</v>
+        <v>2.1647887323943662</v>
       </c>
       <c r="G10" s="4">
         <f>G25/G9</f>
-        <v>2.480216684392067</v>
+        <v>2.5971554793043978</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" ref="H10:K10" si="1">H25/H9</f>
-        <v>2.8682203726806899</v>
+        <v>2.9979471282615515</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="1"/>
-        <v>3.1027603867472324</v>
+        <v>3.2377044249199645</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="1"/>
-        <v>3.1915106504389725</v>
+        <v>3.3243297016930513</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" si="1"/>
-        <v>3.2399363621340047</v>
+        <v>3.3702367110557732</v>
       </c>
       <c r="L10" s="31">
         <f>(K10/F10)^(1/5)-1</f>
-        <v>8.6570160774116056E-2</v>
+        <v>9.2569259949247806E-2</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1085,28 +1086,28 @@
         <v>393.22032000000002</v>
       </c>
       <c r="G13" s="12">
-        <f>F13*1.18</f>
-        <v>463.99997759999997</v>
+        <f>F13*1.22</f>
+        <v>479.72879039999998</v>
       </c>
       <c r="H13" s="12">
         <f>G13*1.17</f>
-        <v>542.87997379199987</v>
+        <v>561.28268476799997</v>
       </c>
       <c r="I13" s="12">
         <f>H13*1.1</f>
-        <v>597.16797117119995</v>
+        <v>617.4109532448</v>
       </c>
       <c r="J13" s="12">
         <f>I13*1.1</f>
-        <v>656.88476828831995</v>
+        <v>679.15204856928005</v>
       </c>
       <c r="K13" s="12">
         <f>J13*1.08</f>
-        <v>709.43554975138557</v>
+        <v>733.48421245482245</v>
       </c>
       <c r="L13" s="31">
         <f t="shared" ref="L13:L17" si="2">(K13/F13)^(1/5)-1</f>
-        <v>0.12526652375986003</v>
+        <v>0.13279406154107476</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1126,27 +1127,27 @@
       </c>
       <c r="F14" s="13">
         <f t="shared" si="3"/>
-        <v>0.64724693701524727</v>
+        <v>0.63959063109954462</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="3"/>
-        <v>0.67217741963452315</v>
+        <v>0.6636718812886685</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="3"/>
-        <v>0.69393822944247896</v>
+        <v>0.68641566139331112</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="3"/>
-        <v>0.70563120282421421</v>
+        <v>0.69914400756658635</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="3"/>
-        <v>0.71867593570076693</v>
+        <v>0.71335077045598505</v>
       </c>
       <c r="K14" s="13">
         <f t="shared" si="3"/>
-        <v>0.72816093791359393</v>
+        <v>0.72373783345616949</v>
       </c>
       <c r="L14" s="31"/>
     </row>
@@ -1168,11 +1169,11 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="4"/>
-        <v>0.17999999999999994</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>0.16999999999999971</v>
+        <v>0.16999999999999993</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
@@ -1206,28 +1207,28 @@
         <v>212.35121999999998</v>
       </c>
       <c r="G17" s="12">
-        <f>F17*1.05</f>
-        <v>222.96878099999998</v>
+        <f>F17*1.135</f>
+        <v>241.01863469999998</v>
       </c>
       <c r="H17" s="12">
         <f>G17*1.05</f>
-        <v>234.11722004999999</v>
+        <v>253.06956643499998</v>
       </c>
       <c r="I17" s="12">
         <f>H17*1.03</f>
-        <v>241.14073665149999</v>
+        <v>260.66165342804999</v>
       </c>
       <c r="J17" s="12">
         <f>I17*1.02</f>
-        <v>245.96355138453001</v>
+        <v>265.874886496611</v>
       </c>
       <c r="K17" s="12">
         <f>J17*1.02</f>
-        <v>250.88282241222061</v>
+        <v>271.1923842265432</v>
       </c>
       <c r="L17" s="31">
         <f t="shared" si="2"/>
-        <v>3.391118419521022E-2</v>
+        <v>5.013357922494488E-2</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1247,27 +1248,27 @@
       </c>
       <c r="F18" s="13">
         <f t="shared" si="5"/>
-        <v>0.34953350507535036</v>
+        <v>0.34539886141834741</v>
       </c>
       <c r="G18" s="13">
         <f t="shared" si="5"/>
-        <v>0.32300557566155169</v>
+        <v>0.33343275183380644</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="5"/>
-        <v>0.29926115717382967</v>
+        <v>0.30948917281280558</v>
       </c>
       <c r="I18" s="13">
         <f t="shared" si="5"/>
-        <v>0.28493897239598187</v>
+        <v>0.29516812430822287</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="5"/>
-        <v>0.26910060024709492</v>
+        <v>0.27926302442406264</v>
       </c>
       <c r="K18" s="13">
         <f t="shared" si="5"/>
-        <v>0.25750481680557397</v>
+        <v>0.26758883869231259</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="G19" s="13">
         <f t="shared" si="6"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="6"/>
@@ -1335,28 +1336,28 @@
         <v>1.95597</v>
       </c>
       <c r="G21" s="12">
-        <f>F21*1.7</f>
-        <v>3.3251489999999997</v>
+        <f>F21*1.07</f>
+        <v>2.0928879</v>
       </c>
       <c r="H21" s="12">
         <f>G21*1.6</f>
-        <v>5.3202384</v>
+        <v>3.34862064</v>
       </c>
       <c r="I21" s="12">
         <f>H21*1.5</f>
-        <v>7.9803575999999996</v>
+        <v>5.0229309600000001</v>
       </c>
       <c r="J21" s="12">
         <f>I21*1.4</f>
-        <v>11.172500639999999</v>
+        <v>7.0321033439999994</v>
       </c>
       <c r="K21" s="12">
         <f>J21*1.25</f>
-        <v>13.965625799999998</v>
+        <v>8.7901291799999992</v>
       </c>
       <c r="L21" s="31">
         <f t="shared" ref="L21" si="7">(K21/F21)^(1/5)-1</f>
-        <v>0.48162958838159176</v>
+        <v>0.35059959021994969</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1376,27 +1377,27 @@
       </c>
       <c r="F22" s="13">
         <f t="shared" ref="F22" si="8">F21/F30</f>
-        <v>3.2195579094023248E-3</v>
+        <v>3.1814736499674694E-3</v>
       </c>
       <c r="G22" s="13">
         <f t="shared" ref="G22" si="9">G21/G30</f>
-        <v>4.8170047039250439E-3</v>
+        <v>2.8953668775249949E-3</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" ref="H22" si="10">H21/H30</f>
-        <v>6.8006133836913561E-3</v>
+        <v>4.0951657938832937E-3</v>
       </c>
       <c r="I22" s="13">
         <f t="shared" ref="I22" si="11">I21/I30</f>
-        <v>9.429824779803829E-3</v>
+        <v>5.6878681251906638E-3</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" ref="J22" si="12">J21/J30</f>
-        <v>1.222346405213821E-2</v>
+        <v>7.3862051199522988E-3</v>
       </c>
       <c r="K22" s="13">
         <f t="shared" ref="K22" si="13">K21/K30</f>
-        <v>1.4334245280832042E-2</v>
+        <v>8.6733278515178595E-3</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1417,7 +1418,7 @@
       </c>
       <c r="G23" s="30">
         <f t="shared" si="14"/>
-        <v>0.7</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="H23" s="30">
         <f t="shared" si="14"/>
@@ -1463,32 +1464,31 @@
         <v>480.64799999999997</v>
       </c>
       <c r="F25" s="25">
-        <f>F13+F17+F21</f>
-        <v>607.52751000000001</v>
+        <v>614.79999999999995</v>
       </c>
       <c r="G25" s="25">
         <f>G13+G17+G21</f>
-        <v>690.29390760000001</v>
+        <v>722.84031300000004</v>
       </c>
       <c r="H25" s="25">
         <f t="shared" ref="H25:K25" si="16">H13+H17+H21</f>
-        <v>782.31743224199988</v>
+        <v>817.70087184299996</v>
       </c>
       <c r="I25" s="25">
         <f t="shared" si="16"/>
-        <v>846.28906542269999</v>
+        <v>883.0955376328501</v>
       </c>
       <c r="J25" s="25">
         <f t="shared" si="16"/>
-        <v>914.02082031284988</v>
+        <v>952.05903840989106</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="16"/>
-        <v>974.28399796360623</v>
+        <v>1013.4667258613657</v>
       </c>
       <c r="L25" s="31">
         <f t="shared" ref="L25" si="17">(K25/F25)^(1/5)-1</f>
-        <v>9.9066382684483312E-2</v>
+        <v>0.10513447517202223</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1508,27 +1508,27 @@
       </c>
       <c r="F26" s="13">
         <f t="shared" si="18"/>
-        <v>0.26397594497428489</v>
+        <v>0.27910653950500164</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="18"/>
-        <v>0.1362348144530936</v>
+        <v>0.17573245445673402</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="18"/>
-        <v>0.13331064294330131</v>
+        <v>0.13123307753727875</v>
       </c>
       <c r="I26" s="13">
         <f t="shared" si="18"/>
-        <v>8.1771964351308624E-2</v>
+        <v>7.997382422065713E-2</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="18"/>
-        <v>8.0033829642262466E-2</v>
+        <v>7.8092910492899348E-2</v>
       </c>
       <c r="K26" s="13">
         <f t="shared" si="18"/>
-        <v>6.593195287403808E-2</v>
+        <v>6.4499873404948227E-2</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1585,31 +1585,31 @@
       </c>
       <c r="F30" s="14">
         <f t="shared" si="19"/>
-        <v>607.52751000000001</v>
+        <v>614.79999999999995</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="19"/>
-        <v>690.29390760000001</v>
+        <v>722.84031300000004</v>
       </c>
       <c r="H30" s="14">
         <f t="shared" si="19"/>
-        <v>782.31743224199988</v>
+        <v>817.70087184299996</v>
       </c>
       <c r="I30" s="14">
         <f t="shared" si="19"/>
-        <v>846.28906542269999</v>
+        <v>883.0955376328501</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="19"/>
-        <v>914.02082031284988</v>
+        <v>952.05903840989106</v>
       </c>
       <c r="K30" s="14">
         <f t="shared" si="19"/>
-        <v>974.28399796360623</v>
+        <v>1013.4667258613657</v>
       </c>
       <c r="L30" s="31">
-        <f t="shared" ref="L30:L32" si="20">(K30/F30)^(1/5)-1</f>
-        <v>9.9066382684483312E-2</v>
+        <f t="shared" ref="L30" si="20">(K30/F30)^(1/5)-1</f>
+        <v>0.10513447517202223</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1629,24 +1629,24 @@
         <v>210.7</v>
       </c>
       <c r="G32" s="12">
-        <f>G30*0.345</f>
-        <v>238.15139812199999</v>
+        <f>G30*0.355</f>
+        <v>256.60831111499999</v>
       </c>
       <c r="H32" s="12">
-        <f>H30*0.34</f>
-        <v>265.98792696227997</v>
+        <f>H30*0.36</f>
+        <v>294.37231386347997</v>
       </c>
       <c r="I32" s="12">
-        <f>I30*0.335</f>
-        <v>283.50683691660453</v>
+        <f>I30*0.36</f>
+        <v>317.91439354782602</v>
       </c>
       <c r="J32" s="12">
-        <f>J30*0.33</f>
-        <v>301.62687070324046</v>
+        <f>J30*0.35</f>
+        <v>333.22066344346183</v>
       </c>
       <c r="K32" s="12">
-        <f>K30*0.328</f>
-        <v>319.56515133206284</v>
+        <f>K30*0.35</f>
+        <v>354.71335405147801</v>
       </c>
       <c r="L32" s="31"/>
     </row>
@@ -1668,27 +1668,27 @@
       </c>
       <c r="F33" s="13">
         <f t="shared" si="21"/>
-        <v>0.34681557054099488</v>
+        <v>0.34271307742355239</v>
       </c>
       <c r="G33" s="13">
         <f t="shared" si="21"/>
-        <v>0.34499999999999997</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="H33" s="13">
         <f t="shared" si="21"/>
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="I33" s="13">
         <f t="shared" si="21"/>
-        <v>0.33500000000000002</v>
+        <v>0.36</v>
       </c>
       <c r="J33" s="13">
         <f t="shared" si="21"/>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="K33" s="13">
         <f t="shared" si="21"/>
-        <v>0.32800000000000001</v>
+        <v>0.35000000000000003</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,31 +1709,31 @@
       </c>
       <c r="F35" s="14">
         <f t="shared" si="22"/>
-        <v>396.82751000000002</v>
+        <v>404.09999999999997</v>
       </c>
       <c r="G35" s="14">
         <f t="shared" si="22"/>
-        <v>452.14250947800002</v>
+        <v>466.23200188500005</v>
       </c>
       <c r="H35" s="14">
         <f t="shared" si="22"/>
-        <v>516.32950527971991</v>
+        <v>523.32855797951993</v>
       </c>
       <c r="I35" s="14">
         <f t="shared" si="22"/>
-        <v>562.78222850609541</v>
+        <v>565.18114408502402</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="22"/>
-        <v>612.39394960960942</v>
+        <v>618.83837496642923</v>
       </c>
       <c r="K35" s="14">
         <f t="shared" si="22"/>
-        <v>654.71884663154333</v>
+        <v>658.75337180988777</v>
       </c>
       <c r="L35" s="31">
         <f t="shared" ref="L35" si="23">(K35/F35)^(1/5)-1</f>
-        <v>0.10532658110063275</v>
+        <v>0.10267315120119158</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="F36" s="13">
         <f t="shared" si="24"/>
-        <v>0.65318442945900512</v>
+        <v>0.65728692257644761</v>
       </c>
       <c r="G36" s="13">
         <f t="shared" si="24"/>
-        <v>0.65500000000000003</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="H36" s="13">
         <f t="shared" si="24"/>
-        <v>0.66</v>
+        <v>0.6399999999999999</v>
       </c>
       <c r="I36" s="13">
         <f t="shared" si="24"/>
-        <v>0.66499999999999992</v>
+        <v>0.6399999999999999</v>
       </c>
       <c r="J36" s="13">
         <f t="shared" si="24"/>
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="K36" s="13">
         <f t="shared" si="24"/>
-        <v>0.67199999999999993</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1795,23 +1795,23 @@
       </c>
       <c r="G38" s="12">
         <f>G30*0.41</f>
-        <v>283.02050211599999</v>
+        <v>296.36452832999998</v>
       </c>
       <c r="H38" s="12">
         <f>H30*0.4</f>
-        <v>312.92697289679995</v>
+        <v>327.08034873719998</v>
       </c>
       <c r="I38" s="12">
         <f>I30*0.39</f>
-        <v>330.052735514853</v>
+        <v>344.40725967681158</v>
       </c>
       <c r="J38" s="12">
         <f>J30*0.38</f>
-        <v>347.32791171888294</v>
+        <v>361.78243459575862</v>
       </c>
       <c r="K38" s="12">
         <f>K30*0.37</f>
-        <v>360.48507924653433</v>
+        <v>374.98268856870533</v>
       </c>
       <c r="L38" s="31"/>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="F39" s="13">
         <f t="shared" si="25"/>
-        <v>0.42138009519931041</v>
+        <v>0.4163955757970072</v>
       </c>
       <c r="G39" s="13">
         <f t="shared" si="25"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="I39" s="13">
         <f t="shared" si="25"/>
-        <v>0.39</v>
+        <v>0.39000000000000007</v>
       </c>
       <c r="J39" s="13">
         <f t="shared" si="25"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="K39" s="13">
         <f t="shared" si="25"/>
-        <v>0.37000000000000005</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1874,27 +1874,27 @@
       </c>
       <c r="G41" s="26">
         <f>G35-G38</f>
-        <v>169.12200736200003</v>
+        <v>169.86747355500006</v>
       </c>
       <c r="H41" s="26">
         <f>H35-H38</f>
-        <v>203.40253238291996</v>
+        <v>196.24820924231994</v>
       </c>
       <c r="I41" s="26">
         <f>I35-I38</f>
-        <v>232.72949299124241</v>
+        <v>220.77388440821244</v>
       </c>
       <c r="J41" s="26">
         <f>J35-J38</f>
-        <v>265.06603789072648</v>
+        <v>257.05594037067061</v>
       </c>
       <c r="K41" s="26">
         <f>K35-K38</f>
-        <v>294.233767385009</v>
+        <v>283.77068324118244</v>
       </c>
       <c r="L41" s="31">
         <f t="shared" ref="L41" si="26">(K41/F41)^(1/5)-1</f>
-        <v>0.16792450199605158</v>
+        <v>0.15949738175307449</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1915,27 +1915,27 @@
       </c>
       <c r="F42" s="13">
         <f t="shared" si="27"/>
-        <v>0.22287056597651028</v>
+        <v>0.22023422251138583</v>
       </c>
       <c r="G42" s="13">
         <f t="shared" si="27"/>
-        <v>0.24500000000000005</v>
+        <v>0.23500000000000007</v>
       </c>
       <c r="H42" s="13">
         <f t="shared" si="27"/>
-        <v>0.26</v>
+        <v>0.23999999999999994</v>
       </c>
       <c r="I42" s="13">
         <f t="shared" si="27"/>
-        <v>0.27499999999999991</v>
+        <v>0.24999999999999992</v>
       </c>
       <c r="J42" s="13">
         <f t="shared" si="27"/>
-        <v>0.29000000000000004</v>
+        <v>0.27</v>
       </c>
       <c r="K42" s="13">
         <f t="shared" si="27"/>
-        <v>0.30199999999999994</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="F44" s="12">
         <f t="shared" si="28"/>
-        <v>19.440880320000002</v>
+        <v>19.6736</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="28"/>
-        <v>22.089405043199999</v>
+        <v>23.130890016000002</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="28"/>
-        <v>25.034157831743997</v>
+        <v>26.166427898976</v>
       </c>
       <c r="I44" s="12">
         <f t="shared" si="28"/>
-        <v>27.0812500935264</v>
+        <v>28.259057204251203</v>
       </c>
       <c r="J44" s="12">
         <f t="shared" si="28"/>
-        <v>29.248666250011198</v>
+        <v>30.465889229116513</v>
       </c>
       <c r="K44" s="12">
         <f t="shared" si="28"/>
-        <v>31.177087934835399</v>
+        <v>32.430935227563701</v>
       </c>
       <c r="L44" s="31"/>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="F45" s="12">
         <f>(F41-F44)*0.11</f>
-        <v>12.7555031648</v>
+        <v>12.729904000000001</v>
       </c>
       <c r="G45" s="12">
         <f>(G41-G44)*0.135</f>
-        <v>19.849401313038005</v>
+        <v>19.80943877776501</v>
       </c>
       <c r="H45" s="12">
         <f>(H41-H44)*0.145</f>
-        <v>25.863414309920515</v>
+        <v>24.661858294784871</v>
       </c>
       <c r="I45" s="12">
         <f>(I41-I44)*0.15</f>
-        <v>30.8472364346574</v>
+        <v>28.877224080594182</v>
       </c>
       <c r="J45" s="12">
         <f>(J41-J44)*0.16</f>
-        <v>37.730779462514448</v>
+        <v>36.25440818264866</v>
       </c>
       <c r="K45" s="12">
         <f>(K41-K44)*0.17</f>
-        <v>44.719635506529514</v>
+        <v>42.727757162315186</v>
       </c>
       <c r="L45" s="31"/>
     </row>
@@ -2047,27 +2047,27 @@
       </c>
       <c r="F47" s="21">
         <f t="shared" si="29"/>
-        <v>103.2036165152</v>
+        <v>102.99649600000001</v>
       </c>
       <c r="G47" s="21">
         <f t="shared" si="29"/>
-        <v>127.18320100576203</v>
+        <v>126.92714476123506</v>
       </c>
       <c r="H47" s="21">
         <f t="shared" si="29"/>
-        <v>152.50496024125545</v>
+        <v>145.41992304855907</v>
       </c>
       <c r="I47" s="21">
         <f t="shared" si="29"/>
-        <v>174.80100646305863</v>
+        <v>163.63760312336706</v>
       </c>
       <c r="J47" s="21">
         <f t="shared" si="29"/>
-        <v>198.08659217820085</v>
+        <v>190.33564295890545</v>
       </c>
       <c r="K47" s="22">
         <f t="shared" si="29"/>
-        <v>218.33704394364406</v>
+        <v>208.61199085130355</v>
       </c>
       <c r="L47" s="31"/>
     </row>
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F51" s="12">
         <f t="shared" si="31"/>
-        <v>6.3439755000000027</v>
+        <v>6.7075999999999993</v>
       </c>
       <c r="G51" s="12">
         <f t="shared" si="31"/>
-        <v>4.1383198800000001</v>
+        <v>5.4020156500000045</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="31"/>
-        <v>4.601176232099994</v>
+        <v>4.7430279421499959</v>
       </c>
       <c r="I51" s="12">
         <f t="shared" si="31"/>
-        <v>3.1985816590350056</v>
+        <v>3.2697332894925069</v>
       </c>
       <c r="J51" s="12">
         <f t="shared" si="31"/>
-        <v>3.3865877445074943</v>
+        <v>3.4481750388520482</v>
       </c>
       <c r="K51" s="12">
         <f t="shared" si="31"/>
-        <v>3.0131588825378177</v>
+        <v>3.070384372573733</v>
       </c>
       <c r="L51" s="31"/>
     </row>
@@ -2212,31 +2212,31 @@
       </c>
       <c r="F53" s="26">
         <f t="shared" si="32"/>
-        <v>100.81964101519999</v>
+        <v>100.248896</v>
       </c>
       <c r="G53" s="26">
         <f t="shared" si="32"/>
-        <v>127.66488112576202</v>
+        <v>126.14512911123504</v>
       </c>
       <c r="H53" s="26">
         <f t="shared" si="32"/>
-        <v>153.41346400915546</v>
+        <v>146.18657510640907</v>
       </c>
       <c r="I53" s="26">
         <f t="shared" si="32"/>
-        <v>177.85795760402362</v>
+        <v>166.62340263387455</v>
       </c>
       <c r="J53" s="26">
         <f t="shared" si="32"/>
-        <v>201.94105451369336</v>
+        <v>194.12851800005345</v>
       </c>
       <c r="K53" s="26">
         <f t="shared" si="32"/>
-        <v>223.58113703550626</v>
+        <v>213.79885845312984</v>
       </c>
       <c r="L53" s="31">
-        <f t="shared" ref="L44:L53" si="33">(K53/F53)^(1/5)-1</f>
-        <v>0.17267590759370521</v>
+        <f t="shared" ref="L53" si="33">(K53/F53)^(1/5)-1</f>
+        <v>0.16355028448429176</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2300,23 +2300,23 @@
       <c r="F57" s="26"/>
       <c r="G57" s="26">
         <f>G53*G56</f>
-        <v>122.15085253753736</v>
+        <v>120.69674078352068</v>
       </c>
       <c r="H57" s="26">
         <f t="shared" ref="H57:K57" si="35">H53*H56</f>
-        <v>134.38124115984058</v>
+        <v>128.05090824709583</v>
       </c>
       <c r="I57" s="26">
         <f t="shared" si="35"/>
-        <v>142.62596212829536</v>
+        <v>133.61686726806917</v>
       </c>
       <c r="J57" s="26">
         <f t="shared" si="35"/>
-        <v>148.25181550925441</v>
+        <v>142.51636600064089</v>
       </c>
       <c r="K57" s="26">
         <f t="shared" si="35"/>
-        <v>150.26598262780936</v>
+        <v>143.69144005677694</v>
       </c>
       <c r="L57" s="31"/>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C69" s="12">
         <f>K57</f>
-        <v>150.26598262780936</v>
+        <v>143.69144005677694</v>
       </c>
       <c r="F69" s="31"/>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C71" s="12">
         <f>C69*(1+C70)/(C65-C70)</f>
-        <v>2287.9178876040496</v>
+        <v>2187.8153009238913</v>
       </c>
     </row>
     <row r="72" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C72" s="14">
         <f>C71*K56</f>
-        <v>1537.679940763371</v>
+        <v>1470.4022904636918</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C76" s="12">
         <f>SUM(G57:K57)</f>
-        <v>697.67585396273694</v>
+        <v>668.57232235610354</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C77" s="12">
         <f>C72</f>
-        <v>1537.679940763371</v>
+        <v>1470.4022904636918</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2441,7 +2441,7 @@
         <v>56</v>
       </c>
       <c r="C79" s="11">
-        <v>258.3</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C80" s="29">
         <f>C76+C77-C78+C79</f>
-        <v>2612.6557947261081</v>
+        <v>2551.9746128197953</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C85" s="27">
         <f>C80/C84</f>
-        <v>29.19168485727495</v>
+        <v>28.513682824802181</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C88" s="19">
         <f>C85/C87-1</f>
-        <v>1.3353347885819962</v>
+        <v>1.2810946259841747</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">

--- a/OPRA Model.xlsx
+++ b/OPRA Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB0487-47A8-4E8E-8C32-474901C83BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A8A1E-80F5-4EF9-9637-D44CE4ED1490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="360" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30168" yWindow="564" windowWidth="28236" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -65,12 +65,6 @@
     <t>Year</t>
   </si>
   <si>
-    <t>FY2024A</t>
-  </si>
-  <si>
-    <t>FY2025E</t>
-  </si>
-  <si>
     <t>FY2026E</t>
   </si>
   <si>
@@ -212,12 +206,6 @@
     <t>Upside/(Downside)</t>
   </si>
   <si>
-    <t>FY2022A</t>
-  </si>
-  <si>
-    <t>FY2023A</t>
-  </si>
-  <si>
     <t>Technology licensing and other revenue</t>
   </si>
   <si>
@@ -270,6 +258,18 @@
   </si>
   <si>
     <t>CAGR</t>
+  </si>
+  <si>
+    <t>FY2025</t>
+  </si>
+  <si>
+    <t>FY2024</t>
+  </si>
+  <si>
+    <t>FY2023</t>
+  </si>
+  <si>
+    <t>FY2022</t>
   </si>
 </sst>
 </file>
@@ -941,45 +941,45 @@
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="L6" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="7">
         <v>323</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="10" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" ref="C10:F10" si="0">C25/C9</f>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
-        <v>1.5454919614147908</v>
+        <v>1.5454887459807076</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="0"/>
@@ -1040,37 +1040,37 @@
       </c>
       <c r="G10" s="4">
         <f>G25/G9</f>
-        <v>2.5971554793043978</v>
+        <v>2.6277767677493533</v>
       </c>
       <c r="H10" s="4">
         <f t="shared" ref="H10:K10" si="1">H25/H9</f>
-        <v>2.9979471282615515</v>
+        <v>3.0954233799297244</v>
       </c>
       <c r="I10" s="4">
         <f t="shared" si="1"/>
-        <v>3.2377044249199645</v>
+        <v>3.5342247420382353</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="1"/>
-        <v>3.3243297016930513</v>
+        <v>3.7905001299648506</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" si="1"/>
-        <v>3.3702367110557732</v>
+        <v>4.0065819506825884</v>
       </c>
       <c r="L10" s="31">
         <f>(K10/F10)^(1/5)-1</f>
-        <v>9.2569259949247806E-2</v>
+        <v>0.13102369182219831</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="11">
         <v>123.91</v>
@@ -1079,40 +1079,39 @@
         <v>230.98</v>
       </c>
       <c r="E13" s="11">
-        <v>293.44799999999998</v>
+        <v>290.72300000000001</v>
       </c>
       <c r="F13" s="12">
-        <f>E13*1.34</f>
-        <v>393.22032000000002</v>
+        <v>396.04</v>
       </c>
       <c r="G13" s="12">
         <f>F13*1.22</f>
-        <v>479.72879039999998</v>
+        <v>483.16880000000003</v>
       </c>
       <c r="H13" s="12">
         <f>G13*1.17</f>
-        <v>561.28268476799997</v>
+        <v>565.30749600000001</v>
       </c>
       <c r="I13" s="12">
-        <f>H13*1.1</f>
-        <v>617.4109532448</v>
+        <f>H13*1.16</f>
+        <v>655.75669535999998</v>
       </c>
       <c r="J13" s="12">
-        <f>I13*1.1</f>
-        <v>679.15204856928005</v>
+        <f>I13*1.15</f>
+        <v>754.12019966399987</v>
       </c>
       <c r="K13" s="12">
-        <f>J13*1.08</f>
-        <v>733.48421245482245</v>
+        <f>J13*1.13</f>
+        <v>852.15582562031977</v>
       </c>
       <c r="L13" s="31">
         <f t="shared" ref="L13:L17" si="2">(K13/F13)^(1/5)-1</f>
-        <v>0.13279406154107476</v>
+        <v>0.16561732287454189</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" s="13">
         <v>0.626</v>
@@ -1123,37 +1122,37 @@
       </c>
       <c r="E14" s="13">
         <f t="shared" si="3"/>
-        <v>0.61052579018325259</v>
+        <v>0.60485761900105484</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="3"/>
-        <v>0.63959063109954462</v>
+        <v>0.64417696811971381</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="3"/>
-        <v>0.6636718812886685</v>
+        <v>0.66064172279578393</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="3"/>
-        <v>0.68641566139331112</v>
+        <v>0.66956723626998582</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="3"/>
-        <v>0.69914400756658635</v>
+        <v>0.6802649252611227</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="3"/>
-        <v>0.71335077045598505</v>
+        <v>0.69467915520640744</v>
       </c>
       <c r="K14" s="13">
         <f t="shared" si="3"/>
-        <v>0.72373783345616949</v>
+        <v>0.7072873611167132</v>
       </c>
       <c r="L14" s="31"/>
     </row>
     <row r="15" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" ref="D15:K15" si="4">D13/C13-1</f>
@@ -1161,11 +1160,11 @@
       </c>
       <c r="E15" s="13">
         <f t="shared" si="4"/>
-        <v>0.27044765780587054</v>
+        <v>0.25865009957572105</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
-        <v>0.34000000000000008</v>
+        <v>0.3622589200028894</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" si="4"/>
@@ -1177,21 +1176,21 @@
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>0.10000000000000009</v>
+        <v>0.15999999999999992</v>
       </c>
       <c r="J15" s="13">
         <f t="shared" si="4"/>
-        <v>0.10000000000000009</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="K15" s="13">
         <f t="shared" si="4"/>
-        <v>8.0000000000000071E-2</v>
+        <v>0.12999999999999989</v>
       </c>
       <c r="L15" s="31"/>
     </row>
     <row r="17" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" s="11">
         <v>121.96</v>
@@ -1200,40 +1199,39 @@
         <v>162.16800000000001</v>
       </c>
       <c r="E17" s="11">
-        <v>186.273</v>
-      </c>
-      <c r="F17" s="12">
-        <f>E17*1.14</f>
-        <v>212.35121999999998</v>
+        <v>188.99700000000001</v>
+      </c>
+      <c r="F17" s="11">
+        <v>216.83199999999999</v>
       </c>
       <c r="G17" s="12">
         <f>F17*1.135</f>
-        <v>241.01863469999998</v>
+        <v>246.10432</v>
       </c>
       <c r="H17" s="12">
-        <f>G17*1.05</f>
-        <v>253.06956643499998</v>
+        <f>G17*1.12</f>
+        <v>275.63683840000004</v>
       </c>
       <c r="I17" s="12">
-        <f>H17*1.03</f>
-        <v>260.66165342804999</v>
+        <f>H17*1.1</f>
+        <v>303.20052224000005</v>
       </c>
       <c r="J17" s="12">
-        <f>I17*1.02</f>
-        <v>265.874886496611</v>
+        <f>I17*1.07</f>
+        <v>324.42455879680006</v>
       </c>
       <c r="K17" s="12">
-        <f>J17*1.02</f>
-        <v>271.1923842265432</v>
+        <f>J17*1.06</f>
+        <v>343.89003232460806</v>
       </c>
       <c r="L17" s="31">
         <f t="shared" si="2"/>
-        <v>5.013357922494488E-2</v>
+        <v>9.6627777822728245E-2</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="13">
         <v>0.373</v>
@@ -1244,36 +1242,36 @@
       </c>
       <c r="E18" s="13">
         <f t="shared" si="5"/>
-        <v>0.38754556348928948</v>
+        <v>0.39321373065888271</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="5"/>
-        <v>0.34539886141834741</v>
+        <v>0.35268705270006506</v>
       </c>
       <c r="G18" s="13">
         <f t="shared" si="5"/>
-        <v>0.33343275183380644</v>
+        <v>0.33650099499861102</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="5"/>
-        <v>0.30948917281280558</v>
+        <v>0.32647257891957038</v>
       </c>
       <c r="I18" s="13">
         <f t="shared" si="5"/>
-        <v>0.29516812430822287</v>
+        <v>0.31453232892650124</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="5"/>
-        <v>0.27926302442406264</v>
+        <v>0.29885285997323385</v>
       </c>
       <c r="K18" s="13">
         <f t="shared" si="5"/>
-        <v>0.26758883869231259</v>
+        <v>0.28542793015603296</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="13">
         <f t="shared" ref="D19:K19" si="6">D17/C17-1</f>
@@ -1281,11 +1279,11 @@
       </c>
       <c r="E19" s="13">
         <f t="shared" si="6"/>
-        <v>0.14864214888264016</v>
+        <v>0.1654395441764096</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="6"/>
-        <v>0.1399999999999999</v>
+        <v>0.14727747001275149</v>
       </c>
       <c r="G19" s="13">
         <f t="shared" si="6"/>
@@ -1293,19 +1291,19 @@
       </c>
       <c r="H19" s="13">
         <f t="shared" si="6"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="I19" s="13">
         <f t="shared" si="6"/>
-        <v>3.0000000000000027E-2</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="6"/>
-        <v>2.0000000000000018E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="K19" s="13">
         <f t="shared" si="6"/>
-        <v>2.0000000000000018E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1320,7 +1318,7 @@
     </row>
     <row r="21" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C21" s="11">
         <v>5.21</v>
@@ -1331,38 +1329,37 @@
       <c r="E21" s="11">
         <v>0.92700000000000005</v>
       </c>
-      <c r="F21" s="12">
-        <f>E21*2.11</f>
-        <v>1.95597</v>
+      <c r="F21" s="11">
+        <v>1.9530000000000001</v>
       </c>
       <c r="G21" s="12">
         <f>F21*1.07</f>
-        <v>2.0928879</v>
+        <v>2.0897100000000002</v>
       </c>
       <c r="H21" s="12">
         <f>G21*1.6</f>
-        <v>3.34862064</v>
+        <v>3.3435360000000003</v>
       </c>
       <c r="I21" s="12">
         <f>H21*1.5</f>
-        <v>5.0229309600000001</v>
+        <v>5.0153040000000004</v>
       </c>
       <c r="J21" s="12">
         <f>I21*1.4</f>
-        <v>7.0321033439999994</v>
+        <v>7.0214255999999997</v>
       </c>
       <c r="K21" s="12">
         <f>J21*1.25</f>
-        <v>8.7901291799999992</v>
+        <v>8.776781999999999</v>
       </c>
       <c r="L21" s="31">
         <f t="shared" ref="L21" si="7">(K21/F21)^(1/5)-1</f>
-        <v>0.35059959021994969</v>
+        <v>0.35059959021994946</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C22" s="13">
         <v>0.373</v>
@@ -1373,36 +1370,36 @@
       </c>
       <c r="E22" s="13">
         <f>E21/E30</f>
-        <v>1.9286463274579321E-3</v>
+        <v>1.9286503400624574E-3</v>
       </c>
       <c r="F22" s="13">
         <f t="shared" ref="F22" si="8">F21/F30</f>
-        <v>3.1814736499674694E-3</v>
+        <v>3.1766428106701368E-3</v>
       </c>
       <c r="G22" s="13">
         <f t="shared" ref="G22" si="9">G21/G30</f>
-        <v>2.8953668775249949E-3</v>
+        <v>2.8572822056051168E-3</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" ref="H22" si="10">H21/H30</f>
-        <v>4.0951657938832937E-3</v>
+        <v>3.9601848104437723E-3</v>
       </c>
       <c r="I22" s="13">
         <f t="shared" ref="I22" si="11">I21/I30</f>
-        <v>5.6878681251906638E-3</v>
+        <v>5.2027458123760691E-3</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" ref="J22" si="12">J21/J30</f>
-        <v>7.3862051199522988E-3</v>
+        <v>6.4679848203587249E-3</v>
       </c>
       <c r="K22" s="13">
         <f t="shared" ref="K22" si="13">K21/K30</f>
-        <v>8.6733278515178595E-3</v>
+        <v>7.2847087272539836E-3</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" s="30">
         <f>D21/C21-1</f>
@@ -1414,7 +1411,7 @@
       </c>
       <c r="F23" s="30">
         <f t="shared" ref="F23:K23" si="14">F21/E21-1</f>
-        <v>1.1099999999999999</v>
+        <v>1.1067961165048543</v>
       </c>
       <c r="G23" s="30">
         <f t="shared" si="14"/>
@@ -1449,7 +1446,7 @@
     </row>
     <row r="25" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C25" s="25">
         <f>C13+C17+C21</f>
@@ -1461,39 +1458,39 @@
       </c>
       <c r="E25" s="25">
         <f>E21+E17+E13</f>
-        <v>480.64799999999997</v>
+        <v>480.64700000000005</v>
       </c>
       <c r="F25" s="25">
         <v>614.79999999999995</v>
       </c>
       <c r="G25" s="25">
         <f>G13+G17+G21</f>
-        <v>722.84031300000004</v>
+        <v>731.36283000000003</v>
       </c>
       <c r="H25" s="25">
         <f t="shared" ref="H25:K25" si="16">H13+H17+H21</f>
-        <v>817.70087184299996</v>
+        <v>844.28787040000009</v>
       </c>
       <c r="I25" s="25">
         <f t="shared" si="16"/>
-        <v>883.0955376328501</v>
+        <v>963.97252160000005</v>
       </c>
       <c r="J25" s="25">
         <f t="shared" si="16"/>
-        <v>952.05903840989106</v>
+        <v>1085.5661840608</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="16"/>
-        <v>1013.4667258613657</v>
+        <v>1204.8226399449277</v>
       </c>
       <c r="L25" s="31">
         <f t="shared" ref="L25" si="17">(K25/F25)^(1/5)-1</f>
-        <v>0.10513447517202223</v>
+        <v>0.1440311565484742</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26" s="13">
         <v>0.252</v>
@@ -1504,72 +1501,72 @@
       </c>
       <c r="E26" s="13">
         <f t="shared" si="18"/>
-        <v>0.2112280666386106</v>
+        <v>0.21122554664879156</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="18"/>
-        <v>0.27910653950500164</v>
+        <v>0.27910920072319167</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="18"/>
-        <v>0.17573245445673402</v>
+        <v>0.18959471372804182</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="18"/>
-        <v>0.13123307753727875</v>
+        <v>0.15440358159847967</v>
       </c>
       <c r="I26" s="13">
         <f t="shared" si="18"/>
-        <v>7.997382422065713E-2</v>
+        <v>0.1417581081003767</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="18"/>
-        <v>7.8092910492899348E-2</v>
+        <v>0.12613810013897386</v>
       </c>
       <c r="K26" s="13">
         <f t="shared" si="18"/>
-        <v>6.4499873404948227E-2</v>
+        <v>0.10985645798031651</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="I28" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="J28" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="K28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="L28" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C30" s="14">
         <f t="shared" ref="C30:K30" si="19">C25</f>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="E30" s="14">
         <f t="shared" si="19"/>
-        <v>480.64799999999997</v>
+        <v>480.64700000000005</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="19"/>
@@ -1589,32 +1586,32 @@
       </c>
       <c r="G30" s="14">
         <f t="shared" si="19"/>
-        <v>722.84031300000004</v>
+        <v>731.36283000000003</v>
       </c>
       <c r="H30" s="14">
         <f t="shared" si="19"/>
-        <v>817.70087184299996</v>
+        <v>844.28787040000009</v>
       </c>
       <c r="I30" s="14">
         <f t="shared" si="19"/>
-        <v>883.0955376328501</v>
+        <v>963.97252160000005</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="19"/>
-        <v>952.05903840989106</v>
+        <v>1085.5661840608</v>
       </c>
       <c r="K30" s="14">
         <f t="shared" si="19"/>
-        <v>1013.4667258613657</v>
+        <v>1204.8226399449277</v>
       </c>
       <c r="L30" s="31">
         <f t="shared" ref="L30" si="20">(K30/F30)^(1/5)-1</f>
-        <v>0.10513447517202223</v>
+        <v>0.1440311565484742</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C32" s="12">
         <v>54.6</v>
@@ -1626,33 +1623,33 @@
         <v>132.6</v>
       </c>
       <c r="F32" s="12">
-        <v>210.7</v>
+        <v>220.50399999999999</v>
       </c>
       <c r="G32" s="12">
-        <f>G30*0.355</f>
-        <v>256.60831111499999</v>
+        <f>G30*0.385</f>
+        <v>281.57468955000002</v>
       </c>
       <c r="H32" s="12">
-        <f>H30*0.36</f>
-        <v>294.37231386347997</v>
+        <f>H30*0.385</f>
+        <v>325.05083010400006</v>
       </c>
       <c r="I32" s="12">
-        <f>I30*0.36</f>
-        <v>317.91439354782602</v>
+        <f>I30*0.4</f>
+        <v>385.58900864000003</v>
       </c>
       <c r="J32" s="12">
-        <f>J30*0.35</f>
-        <v>333.22066344346183</v>
+        <f>J30*0.411</f>
+        <v>446.16770164898878</v>
       </c>
       <c r="K32" s="12">
-        <f>K30*0.35</f>
-        <v>354.71335405147801</v>
+        <f>K30*0.42</f>
+        <v>506.02550877686963</v>
       </c>
       <c r="L32" s="31"/>
     </row>
     <row r="33" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C33" s="13">
         <f t="shared" ref="C33:K33" si="21">C32/C30</f>
@@ -1664,36 +1661,36 @@
       </c>
       <c r="E33" s="13">
         <f t="shared" si="21"/>
-        <v>0.27587756528686275</v>
+        <v>0.27587813925812493</v>
       </c>
       <c r="F33" s="13">
         <f t="shared" si="21"/>
-        <v>0.34271307742355239</v>
+        <v>0.35865972674040342</v>
       </c>
       <c r="G33" s="13">
         <f t="shared" si="21"/>
-        <v>0.35499999999999998</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="H33" s="13">
         <f t="shared" si="21"/>
-        <v>0.36</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="I33" s="13">
         <f t="shared" si="21"/>
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="J33" s="13">
         <f t="shared" si="21"/>
-        <v>0.35</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="K33" s="13">
         <f t="shared" si="21"/>
-        <v>0.35000000000000003</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" s="14">
         <f t="shared" ref="C35:K35" si="22">C30-C32</f>
@@ -1705,40 +1702,40 @@
       </c>
       <c r="E35" s="14">
         <f t="shared" si="22"/>
-        <v>348.048</v>
+        <v>348.04700000000003</v>
       </c>
       <c r="F35" s="14">
         <f t="shared" si="22"/>
-        <v>404.09999999999997</v>
+        <v>394.29599999999994</v>
       </c>
       <c r="G35" s="14">
         <f t="shared" si="22"/>
-        <v>466.23200188500005</v>
+        <v>449.78814045000001</v>
       </c>
       <c r="H35" s="14">
         <f t="shared" si="22"/>
-        <v>523.32855797951993</v>
+        <v>519.23704029600003</v>
       </c>
       <c r="I35" s="14">
         <f t="shared" si="22"/>
-        <v>565.18114408502402</v>
+        <v>578.38351295999996</v>
       </c>
       <c r="J35" s="14">
         <f t="shared" si="22"/>
-        <v>618.83837496642923</v>
+        <v>639.39848241181119</v>
       </c>
       <c r="K35" s="14">
         <f t="shared" si="22"/>
-        <v>658.75337180988777</v>
+        <v>698.79713116805806</v>
       </c>
       <c r="L35" s="31">
         <f t="shared" ref="L35" si="23">(K35/F35)^(1/5)-1</f>
-        <v>0.10267315120119158</v>
+        <v>0.12125850015129691</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C36" s="13">
         <f t="shared" ref="C36:K36" si="24">C35/C30</f>
@@ -1750,238 +1747,240 @@
       </c>
       <c r="E36" s="13">
         <f t="shared" si="24"/>
-        <v>0.72412243471313731</v>
+        <v>0.72412186074187501</v>
       </c>
       <c r="F36" s="13">
         <f t="shared" si="24"/>
-        <v>0.65728692257644761</v>
+        <v>0.64134027325959653</v>
       </c>
       <c r="G36" s="13">
         <f t="shared" si="24"/>
-        <v>0.64500000000000002</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="H36" s="13">
         <f t="shared" si="24"/>
-        <v>0.6399999999999999</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="I36" s="13">
         <f t="shared" si="24"/>
-        <v>0.6399999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J36" s="13">
         <f t="shared" si="24"/>
-        <v>0.65</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="K36" s="13">
         <f t="shared" si="24"/>
-        <v>0.65</v>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C38" s="12">
-        <v>201.9</v>
+        <f t="shared" ref="C38:F38" si="25">C35-C41</f>
+        <v>128.39600000000002</v>
       </c>
       <c r="D38" s="12">
-        <v>209.1</v>
+        <f t="shared" si="25"/>
+        <v>209.90800000000002</v>
       </c>
       <c r="E38" s="12">
-        <v>233.3</v>
+        <f t="shared" si="25"/>
+        <v>232.73800000000003</v>
       </c>
       <c r="F38" s="12">
-        <v>256</v>
+        <f>F35-F41</f>
+        <v>251.76599999999993</v>
       </c>
       <c r="G38" s="12">
-        <f>G30*0.41</f>
-        <v>296.36452832999998</v>
+        <f>G30*0.38</f>
+        <v>277.91787540000001</v>
       </c>
       <c r="H38" s="12">
-        <f>H30*0.4</f>
-        <v>327.08034873719998</v>
+        <f>H30*0.375</f>
+        <v>316.60795140000005</v>
       </c>
       <c r="I38" s="12">
-        <f>I30*0.39</f>
-        <v>344.40725967681158</v>
+        <f>I30*0.36</f>
+        <v>347.03010777600002</v>
       </c>
       <c r="J38" s="12">
-        <f>J30*0.38</f>
-        <v>361.78243459575862</v>
+        <f>J30*0.34</f>
+        <v>369.09250258067203</v>
       </c>
       <c r="K38" s="12">
-        <f>K30*0.37</f>
-        <v>374.98268856870533</v>
+        <f>K30*0.325</f>
+        <v>391.5673579821015</v>
       </c>
       <c r="L38" s="31"/>
     </row>
     <row r="39" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C39" s="13">
-        <f t="shared" ref="C39:K39" si="25">C38/C30</f>
-        <v>0.80412617492432692</v>
+        <f t="shared" ref="C39:K39" si="26">C38/C30</f>
+        <v>0.5113748606021985</v>
       </c>
       <c r="D39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.52692987120332035</v>
+        <f t="shared" si="26"/>
+        <v>0.52896602297726725</v>
       </c>
       <c r="E39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.48538639503337166</v>
+        <f t="shared" si="26"/>
+        <v>0.48421814762185139</v>
       </c>
       <c r="F39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.4163955757970072</v>
+        <f t="shared" si="26"/>
+        <v>0.4095087833441769</v>
       </c>
       <c r="G39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.41</v>
+        <f t="shared" si="26"/>
+        <v>0.38</v>
       </c>
       <c r="H39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.4</v>
+        <f t="shared" si="26"/>
+        <v>0.375</v>
       </c>
       <c r="I39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.39000000000000007</v>
+        <f t="shared" si="26"/>
+        <v>0.36</v>
       </c>
       <c r="J39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.38</v>
+        <f t="shared" si="26"/>
+        <v>0.34</v>
       </c>
       <c r="K39" s="13">
-        <f t="shared" si="25"/>
-        <v>0.37</v>
+        <f t="shared" si="26"/>
+        <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="26">
-        <v>68.099999999999994</v>
+        <v>68.084000000000003</v>
       </c>
       <c r="D41" s="26">
-        <v>93.7</v>
+        <v>93.718999999999994</v>
       </c>
       <c r="E41" s="26">
-        <v>115.3</v>
+        <v>115.309</v>
       </c>
       <c r="F41" s="26">
-        <v>135.4</v>
+        <v>142.53</v>
       </c>
       <c r="G41" s="26">
         <f>G35-G38</f>
-        <v>169.86747355500006</v>
+        <v>171.87026505</v>
       </c>
       <c r="H41" s="26">
         <f>H35-H38</f>
-        <v>196.24820924231994</v>
+        <v>202.62908889599998</v>
       </c>
       <c r="I41" s="26">
         <f>I35-I38</f>
-        <v>220.77388440821244</v>
+        <v>231.35340518399994</v>
       </c>
       <c r="J41" s="26">
         <f>J35-J38</f>
-        <v>257.05594037067061</v>
+        <v>270.30597983113915</v>
       </c>
       <c r="K41" s="26">
         <f>K35-K38</f>
-        <v>283.77068324118244</v>
+        <v>307.22977318595656</v>
       </c>
       <c r="L41" s="31">
-        <f t="shared" ref="L41" si="26">(K41/F41)^(1/5)-1</f>
-        <v>0.15949738175307449</v>
+        <f t="shared" ref="L41" si="27">(K41/F41)^(1/5)-1</f>
+        <v>0.16603450734591063</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" s="13">
-        <f t="shared" ref="C42:K42" si="27">C41/C30</f>
-        <v>0.27122829377090962</v>
+        <f t="shared" ref="C42:K42" si="28">C41/C30</f>
+        <v>0.27116456906165365</v>
       </c>
       <c r="D42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.23612304606289392</v>
+        <f t="shared" si="28"/>
+        <v>0.23617092586945948</v>
       </c>
       <c r="E42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.23988448927281505</v>
+        <f t="shared" si="28"/>
+        <v>0.23990371312002359</v>
       </c>
       <c r="F42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.22023422251138583</v>
+        <f t="shared" si="28"/>
+        <v>0.23183148991541966</v>
       </c>
       <c r="G42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.23500000000000007</v>
+        <f t="shared" si="28"/>
+        <v>0.23499999999999999</v>
       </c>
       <c r="H42" s="13">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
+        <v>0.23999999999999996</v>
+      </c>
+      <c r="I42" s="13">
+        <f t="shared" si="28"/>
         <v>0.23999999999999994</v>
       </c>
-      <c r="I42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.24999999999999992</v>
-      </c>
       <c r="J42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.27</v>
+        <f t="shared" si="28"/>
+        <v>0.24899999999999997</v>
       </c>
       <c r="K42" s="13">
-        <f t="shared" si="27"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="28"/>
+        <v>0.255</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C44" s="12">
-        <v>17.600000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="D44" s="12">
-        <f t="shared" ref="D44:K44" si="28">D30*0.032</f>
-        <v>12.698464</v>
+        <v>13.2</v>
       </c>
       <c r="E44" s="12">
-        <f t="shared" si="28"/>
-        <v>15.380735999999999</v>
+        <v>15.6</v>
       </c>
       <c r="F44" s="12">
-        <f t="shared" si="28"/>
-        <v>19.6736</v>
+        <f>E44*1.1</f>
+        <v>17.16</v>
       </c>
       <c r="G44" s="12">
-        <f t="shared" si="28"/>
-        <v>23.130890016000002</v>
+        <f t="shared" ref="G44" si="29">F44*1.1</f>
+        <v>18.876000000000001</v>
       </c>
       <c r="H44" s="12">
-        <f t="shared" si="28"/>
-        <v>26.166427898976</v>
+        <f t="shared" ref="H44" si="30">G44*1.1</f>
+        <v>20.763600000000004</v>
       </c>
       <c r="I44" s="12">
-        <f t="shared" si="28"/>
-        <v>28.259057204251203</v>
+        <f>H44*1.08</f>
+        <v>22.424688000000007</v>
       </c>
       <c r="J44" s="12">
-        <f t="shared" si="28"/>
-        <v>30.465889229116513</v>
+        <f>I44*1.08</f>
+        <v>24.21866304000001</v>
       </c>
       <c r="K44" s="12">
-        <f t="shared" si="28"/>
-        <v>32.430935227563701</v>
+        <f>J44*1.07</f>
+        <v>25.913969452800011</v>
       </c>
       <c r="L44" s="31"/>
     </row>
     <row r="45" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C45" s="12">
         <v>9</v>
@@ -1994,27 +1993,27 @@
       </c>
       <c r="F45" s="12">
         <f>(F41-F44)*0.11</f>
-        <v>12.729904000000001</v>
+        <v>13.790700000000001</v>
       </c>
       <c r="G45" s="12">
         <f>(G41-G44)*0.135</f>
-        <v>19.80943877776501</v>
+        <v>20.65422578175</v>
       </c>
       <c r="H45" s="12">
         <f>(H41-H44)*0.145</f>
-        <v>24.661858294784871</v>
+        <v>26.370495889919997</v>
       </c>
       <c r="I45" s="12">
         <f>(I41-I44)*0.15</f>
-        <v>28.877224080594182</v>
+        <v>31.339307577599989</v>
       </c>
       <c r="J45" s="12">
         <f>(J41-J44)*0.16</f>
-        <v>36.25440818264866</v>
+        <v>39.373970686582261</v>
       </c>
       <c r="K45" s="12">
         <f>(K41-K44)*0.17</f>
-        <v>42.727757162315186</v>
+        <v>47.823686634636616</v>
       </c>
       <c r="L45" s="31"/>
     </row>
@@ -2031,43 +2030,43 @@
     </row>
     <row r="47" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C47" s="21">
-        <f t="shared" ref="C47:K47" si="29">C41-C44-C45</f>
-        <v>41.499999999999993</v>
+        <f t="shared" ref="C47:K47" si="31">C41-C44-C45</f>
+        <v>43.884</v>
       </c>
       <c r="D47" s="21">
-        <f t="shared" si="29"/>
-        <v>74.301535999999999</v>
+        <f t="shared" si="31"/>
+        <v>73.818999999999988</v>
       </c>
       <c r="E47" s="21">
-        <f t="shared" si="29"/>
-        <v>82.319264000000004</v>
+        <f t="shared" si="31"/>
+        <v>82.109000000000009</v>
       </c>
       <c r="F47" s="21">
-        <f t="shared" si="29"/>
-        <v>102.99649600000001</v>
+        <f t="shared" si="31"/>
+        <v>111.5793</v>
       </c>
       <c r="G47" s="21">
-        <f t="shared" si="29"/>
-        <v>126.92714476123506</v>
+        <f t="shared" si="31"/>
+        <v>132.34003926825</v>
       </c>
       <c r="H47" s="21">
-        <f t="shared" si="29"/>
-        <v>145.41992304855907</v>
+        <f t="shared" si="31"/>
+        <v>155.49499300607999</v>
       </c>
       <c r="I47" s="21">
-        <f t="shared" si="29"/>
-        <v>163.63760312336706</v>
+        <f t="shared" si="31"/>
+        <v>177.58940960639995</v>
       </c>
       <c r="J47" s="21">
-        <f t="shared" si="29"/>
-        <v>190.33564295890545</v>
+        <f t="shared" si="31"/>
+        <v>206.71334610455688</v>
       </c>
       <c r="K47" s="22">
-        <f t="shared" si="29"/>
-        <v>208.61199085130355</v>
+        <f t="shared" si="31"/>
+        <v>233.49211709851994</v>
       </c>
       <c r="L47" s="31"/>
     </row>
@@ -2078,7 +2077,7 @@
     </row>
     <row r="49" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C49" s="12">
         <v>15.2</v>
@@ -2090,34 +2089,33 @@
         <v>15.6</v>
       </c>
       <c r="F49" s="12">
-        <f>E49*1.1</f>
-        <v>17.16</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="G49" s="12">
-        <f t="shared" ref="G49:H49" si="30">F49*1.1</f>
-        <v>18.876000000000001</v>
+        <f t="shared" ref="G49:H49" si="32">F49*1.1</f>
+        <v>20.79</v>
       </c>
       <c r="H49" s="12">
-        <f t="shared" si="30"/>
-        <v>20.763600000000004</v>
+        <f t="shared" si="32"/>
+        <v>22.869</v>
       </c>
       <c r="I49" s="12">
         <f>H49*1.08</f>
-        <v>22.424688000000007</v>
+        <v>24.698520000000002</v>
       </c>
       <c r="J49" s="12">
         <f>I49*1.08</f>
-        <v>24.21866304000001</v>
+        <v>26.674401600000003</v>
       </c>
       <c r="K49" s="12">
         <f>J49*1.07</f>
-        <v>25.913969452800011</v>
+        <v>28.541609712000003</v>
       </c>
       <c r="L49" s="31"/>
     </row>
     <row r="50" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C50" s="12">
         <v>9.5</v>
@@ -2129,119 +2127,119 @@
         <v>23.3</v>
       </c>
       <c r="F50" s="12">
-        <v>13.2</v>
+        <v>6</v>
       </c>
       <c r="G50" s="12">
-        <f>F50*1.08</f>
-        <v>14.256</v>
+        <f>F50*2.2</f>
+        <v>13.200000000000001</v>
       </c>
       <c r="H50" s="12">
         <f>G50*1.07</f>
-        <v>15.253920000000001</v>
+        <v>14.124000000000002</v>
       </c>
       <c r="I50" s="12">
-        <f>H50*1.06</f>
-        <v>16.169155200000002</v>
+        <f>H50*0.8</f>
+        <v>11.299200000000003</v>
       </c>
       <c r="J50" s="12">
         <f>I50*1.05</f>
-        <v>16.977612960000002</v>
+        <v>11.864160000000004</v>
       </c>
       <c r="K50" s="12">
-        <f>J50*1.04</f>
-        <v>17.656717478400001</v>
+        <f>J50*1.05</f>
+        <v>12.457368000000004</v>
       </c>
       <c r="L50" s="31"/>
     </row>
     <row r="51" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51" s="12">
         <v>6.1</v>
       </c>
       <c r="D51" s="12">
-        <f t="shared" ref="D51:K51" si="31">(D30-C30)*0.05</f>
+        <f t="shared" ref="D51:K51" si="33">(D30-C30)*0.05</f>
         <v>7.28735</v>
       </c>
       <c r="E51" s="12">
-        <f t="shared" si="31"/>
-        <v>4.1910499999999988</v>
+        <f t="shared" si="33"/>
+        <v>4.1910000000000025</v>
       </c>
       <c r="F51" s="12">
-        <f t="shared" si="31"/>
-        <v>6.7075999999999993</v>
+        <f t="shared" si="33"/>
+        <v>6.7076499999999957</v>
       </c>
       <c r="G51" s="12">
-        <f t="shared" si="31"/>
-        <v>5.4020156500000045</v>
+        <f t="shared" si="33"/>
+        <v>5.8281415000000045</v>
       </c>
       <c r="H51" s="12">
-        <f t="shared" si="31"/>
-        <v>4.7430279421499959</v>
+        <f t="shared" si="33"/>
+        <v>5.646252020000003</v>
       </c>
       <c r="I51" s="12">
-        <f t="shared" si="31"/>
-        <v>3.2697332894925069</v>
+        <f t="shared" si="33"/>
+        <v>5.9842325599999988</v>
       </c>
       <c r="J51" s="12">
-        <f t="shared" si="31"/>
-        <v>3.4481750388520482</v>
+        <f t="shared" si="33"/>
+        <v>6.0796831230399961</v>
       </c>
       <c r="K51" s="12">
-        <f t="shared" si="31"/>
-        <v>3.070384372573733</v>
+        <f t="shared" si="33"/>
+        <v>5.9628227942063861</v>
       </c>
       <c r="L51" s="31"/>
     </row>
     <row r="53" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C53" s="26">
-        <f t="shared" ref="C53:K53" si="32">C47+C49-C50-C51</f>
-        <v>41.099999999999987</v>
+        <f t="shared" ref="C53:K53" si="34">C47+C49-C50-C51</f>
+        <v>43.484000000000002</v>
       </c>
       <c r="D53" s="26">
-        <f t="shared" si="32"/>
-        <v>73.814185999999992</v>
+        <f t="shared" si="34"/>
+        <v>73.331649999999982</v>
       </c>
       <c r="E53" s="26">
-        <f t="shared" si="32"/>
-        <v>70.428213999999997</v>
+        <f t="shared" si="34"/>
+        <v>70.218000000000004</v>
       </c>
       <c r="F53" s="26">
-        <f t="shared" si="32"/>
-        <v>100.248896</v>
+        <f t="shared" si="34"/>
+        <v>117.77164999999999</v>
       </c>
       <c r="G53" s="26">
-        <f t="shared" si="32"/>
-        <v>126.14512911123504</v>
+        <f t="shared" si="34"/>
+        <v>134.10189776824998</v>
       </c>
       <c r="H53" s="26">
-        <f t="shared" si="32"/>
-        <v>146.18657510640907</v>
+        <f t="shared" si="34"/>
+        <v>158.59374098608001</v>
       </c>
       <c r="I53" s="26">
-        <f t="shared" si="32"/>
-        <v>166.62340263387455</v>
+        <f t="shared" si="34"/>
+        <v>185.00449704639993</v>
       </c>
       <c r="J53" s="26">
-        <f t="shared" si="32"/>
-        <v>194.12851800005345</v>
+        <f t="shared" si="34"/>
+        <v>215.4439045815169</v>
       </c>
       <c r="K53" s="26">
-        <f t="shared" si="32"/>
-        <v>213.79885845312984</v>
+        <f t="shared" si="34"/>
+        <v>243.61353601631359</v>
       </c>
       <c r="L53" s="31">
-        <f t="shared" ref="L53" si="33">(K53/F53)^(1/5)-1</f>
-        <v>0.16355028448429176</v>
+        <f t="shared" ref="L53" si="35">(K53/F53)^(1/5)-1</f>
+        <v>0.15646403509775264</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -2264,35 +2262,35 @@
     </row>
     <row r="56" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
       <c r="G56" s="15">
-        <f t="shared" ref="G56:K56" si="34">1/(1+$C$65)^G55</f>
+        <f t="shared" ref="G56:K56" si="36">1/(1+$C$65)^G55</f>
         <v>0.95680857147555853</v>
       </c>
       <c r="H56" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.87594163933239222</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.80190936660721424</v>
       </c>
       <c r="J56" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.73413410594625594</v>
       </c>
       <c r="K56" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.67208703122368529</v>
       </c>
       <c r="L56" s="15"/>
     </row>
     <row r="57" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C57" s="24"/>
       <c r="D57" s="26"/>
@@ -2300,36 +2298,36 @@
       <c r="F57" s="26"/>
       <c r="G57" s="26">
         <f>G53*G56</f>
-        <v>120.69674078352068</v>
+        <v>128.30984523580065</v>
       </c>
       <c r="H57" s="26">
-        <f t="shared" ref="H57:K57" si="35">H53*H56</f>
-        <v>128.05090824709583</v>
+        <f t="shared" ref="H57:K57" si="37">H53*H56</f>
+        <v>138.91886146720373</v>
       </c>
       <c r="I57" s="26">
-        <f t="shared" si="35"/>
-        <v>133.61686726806917</v>
+        <f t="shared" si="37"/>
+        <v>148.35683904596482</v>
       </c>
       <c r="J57" s="26">
-        <f t="shared" si="35"/>
-        <v>142.51636600064089</v>
+        <f t="shared" si="37"/>
+        <v>158.16471827152239</v>
       </c>
       <c r="K57" s="26">
-        <f t="shared" si="35"/>
-        <v>143.69144005677694</v>
+        <f t="shared" si="37"/>
+        <v>163.72949818710853</v>
       </c>
       <c r="L57" s="31"/>
     </row>
     <row r="60" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="2:12" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C62" s="1">
         <v>4.24E-2</v>
@@ -2337,7 +2335,7 @@
     </row>
     <row r="63" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" s="17">
         <v>1.2</v>
@@ -2345,7 +2343,7 @@
     </row>
     <row r="64" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C64" s="1">
         <v>4.1599999999999998E-2</v>
@@ -2353,7 +2351,7 @@
     </row>
     <row r="65" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C65" s="16">
         <f>C62+(C63*C64)</f>
@@ -2362,24 +2360,24 @@
     </row>
     <row r="67" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="2:6" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C69" s="12">
         <f>K57</f>
-        <v>143.69144005677694</v>
+        <v>163.72949818710853</v>
       </c>
       <c r="F69" s="31"/>
     </row>
     <row r="70" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C70" s="18">
         <v>2.5000000000000001E-2</v>
@@ -2387,50 +2385,50 @@
     </row>
     <row r="71" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C71" s="12">
         <f>C69*(1+C70)/(C65-C70)</f>
-        <v>2187.8153009238913</v>
+        <v>2492.9105116129867</v>
       </c>
     </row>
     <row r="72" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C72" s="14">
         <f>C71*K56</f>
-        <v>1470.4022904636918</v>
+        <v>1675.4528248562906</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="2:6" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C76" s="12">
         <f>SUM(G57:K57)</f>
-        <v>668.57232235610354</v>
+        <v>737.47976220760017</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C77" s="12">
         <f>C72</f>
-        <v>1470.4022904636918</v>
+        <v>1675.4528248562906</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C78" s="11">
         <v>-119</v>
@@ -2438,7 +2436,7 @@
     </row>
     <row r="79" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C79" s="11">
         <v>294</v>
@@ -2446,11 +2444,11 @@
     </row>
     <row r="80" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C80" s="29">
         <f>C76+C77-C78+C79</f>
-        <v>2551.9746128197953</v>
+        <v>2825.9325870638909</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2459,20 +2457,20 @@
     </row>
     <row r="82" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="34"/>
       <c r="B83" s="35" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C83" s="35"/>
     </row>
     <row r="84" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C84" s="12">
         <v>89.5</v>
@@ -2480,11 +2478,11 @@
     </row>
     <row r="85" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C85" s="27">
         <f>C80/C84</f>
-        <v>28.513682824802181</v>
+        <v>31.574665777250178</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2492,7 +2490,7 @@
     </row>
     <row r="87" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C87" s="9">
         <v>12.5</v>
@@ -2500,11 +2498,11 @@
     </row>
     <row r="88" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C88" s="19">
         <f>C85/C87-1</f>
-        <v>1.2810946259841747</v>
+        <v>1.5259732621800142</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2530,22 +2528,22 @@
     </row>
     <row r="2" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B2" s="38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
       <c r="E2" s="32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E3" s="31">
         <v>0.53300000000000003</v>
@@ -2558,7 +2556,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E4" s="31">
         <v>9.7000000000000003E-2</v>
@@ -2570,7 +2568,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E5" s="31">
         <v>4.1000000000000002E-2</v>
@@ -2582,7 +2580,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E6" s="31">
         <v>3.5000000000000003E-2</v>
@@ -2594,7 +2592,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E7" s="31">
         <v>3.1E-2</v>
@@ -2606,7 +2604,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E8" s="31">
         <v>0.02</v>
@@ -2618,7 +2616,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E9" s="31">
         <v>1.7999999999999999E-2</v>
@@ -2630,7 +2628,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E10" s="31">
         <v>1.7000000000000001E-2</v>
@@ -2642,7 +2640,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="31">
         <f>1-(SUM(E3:E10))</f>
